--- a/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
+++ b/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\muhunthancanagey-servocontrol\Design Files\Control-Boards-v2.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="681">
   <si>
     <t>#</t>
   </si>
@@ -1992,14 +1992,83 @@
     <t>R310, R319, R329, R330, R331, R332</t>
   </si>
   <si>
-    <t>C33, C34, C36, C50, C97</t>
+    <t>C33, C34, C36, C97</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 10V X5R 0402</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB105</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>Shunt Jumper</t>
+  </si>
+  <si>
+    <t>Open top 3A 2.54mm P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t>TC2030-CTX 6-Pin Cable for ARM Cortex ATMEL</t>
+  </si>
+  <si>
+    <t>TC2030-CTX</t>
+  </si>
+  <si>
+    <t>Qty: 2 cables per whole order</t>
+  </si>
+  <si>
+    <t>0287003.PXCN</t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 3A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>SIRON D021</t>
+  </si>
+  <si>
+    <t>SIRON</t>
+  </si>
+  <si>
+    <t>Siron</t>
+  </si>
+  <si>
+    <t>Photoelectric Sensor</t>
+  </si>
+  <si>
+    <t>led induction light</t>
+  </si>
+  <si>
+    <t>SiRON K070-8-1</t>
+  </si>
+  <si>
+    <t>Reed Sensor</t>
+  </si>
+  <si>
+    <t>Client have not provided any details of this</t>
+  </si>
+  <si>
+    <t>VDF</t>
+  </si>
+  <si>
+    <t>Should be provided by client for testing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2062,6 +2131,29 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2179,10 +2271,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2234,8 +2327,30 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2521,7 +2636,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K156"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2534,6 +2649,8 @@
     <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2745,7 +2862,7 @@
     <row r="8" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B71" si="1">ROW(B8) - ROW($B$2)</f>
+        <f t="shared" ref="B8:B72" si="1">ROW(B8) - ROW($B$2)</f>
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -3026,7 +3143,7 @@
         <v>584</v>
       </c>
       <c r="J16" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K16" s="9"/>
     </row>
@@ -3135,28 +3252,28 @@
       <c r="C20" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="D20" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="J20" s="7">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7"/>
+      <c r="I20" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="J20" s="9">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -3167,28 +3284,28 @@
       <c r="C21" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="J21" s="9">
-        <v>8</v>
-      </c>
-      <c r="K21" s="9"/>
+      <c r="D21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="J21" s="7">
+        <v>1</v>
+      </c>
+      <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -3199,28 +3316,28 @@
       <c r="C22" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="D22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="J22" s="7">
-        <v>2</v>
-      </c>
-      <c r="K22" s="7"/>
+      <c r="G22" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="J22" s="9">
+        <v>8</v>
+      </c>
+      <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -3232,22 +3349,22 @@
         <v>2</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>340</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>535</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -3263,28 +3380,28 @@
       <c r="C24" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="H24" s="9" t="s">
+      <c r="D24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>595</v>
-      </c>
-      <c r="J24" s="9">
-        <v>1</v>
-      </c>
-      <c r="K24" s="9"/>
+      <c r="I24" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="J24" s="7">
+        <v>2</v>
+      </c>
+      <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -3295,28 +3412,28 @@
       <c r="C25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="D25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="J25" s="7">
-        <v>1</v>
-      </c>
-      <c r="K25" s="7"/>
+      <c r="G25" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -3327,28 +3444,28 @@
       <c r="C26" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="F26" s="9" t="s">
+      <c r="D26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>597</v>
-      </c>
-      <c r="J26" s="9">
-        <v>1</v>
-      </c>
-      <c r="K26" s="9"/>
+      <c r="G26" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="J26" s="7">
+        <v>1</v>
+      </c>
+      <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -3359,28 +3476,28 @@
       <c r="C27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="J27" s="7">
-        <v>1</v>
-      </c>
-      <c r="K27" s="7"/>
+      <c r="D27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="J27" s="9">
+        <v>1</v>
+      </c>
+      <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3391,28 +3508,28 @@
       <c r="C28" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="H28" s="9" t="s">
+      <c r="D28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>599</v>
-      </c>
-      <c r="J28" s="9">
-        <v>1</v>
-      </c>
-      <c r="K28" s="9"/>
+      <c r="I28" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="J28" s="7">
+        <v>1</v>
+      </c>
+      <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -3423,28 +3540,28 @@
       <c r="C29" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="H29" s="7" t="s">
+      <c r="D29" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="J29" s="7">
-        <v>1</v>
-      </c>
-      <c r="K29" s="7"/>
+      <c r="I29" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="J29" s="9">
+        <v>1</v>
+      </c>
+      <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -3455,28 +3572,28 @@
       <c r="C30" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="H30" s="9" t="s">
+      <c r="D30" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="J30" s="9">
-        <v>6</v>
-      </c>
-      <c r="K30" s="9"/>
+      <c r="I30" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="J30" s="7">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3487,28 +3604,28 @@
       <c r="C31" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="H31" s="7" t="s">
+      <c r="D31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="J31" s="7">
-        <v>1</v>
-      </c>
-      <c r="K31" s="7"/>
+      <c r="I31" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="J31" s="9">
+        <v>6</v>
+      </c>
+      <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3519,28 +3636,28 @@
       <c r="C32" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F32" s="9" t="s">
+      <c r="D32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="H32" s="9" t="s">
+      <c r="G32" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="H32" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>602</v>
-      </c>
-      <c r="J32" s="9">
-        <v>3</v>
-      </c>
-      <c r="K32" s="9"/>
+      <c r="I32" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="J32" s="7">
+        <v>1</v>
+      </c>
+      <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3551,28 +3668,28 @@
       <c r="C33" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="D33" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="J33" s="7">
-        <v>2</v>
-      </c>
-      <c r="K33" s="7"/>
+      <c r="G33" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="J33" s="9">
+        <v>3</v>
+      </c>
+      <c r="K33" s="9"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3583,28 +3700,28 @@
       <c r="C34" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="J34" s="9">
+      <c r="D34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="J34" s="7">
         <v>2</v>
       </c>
-      <c r="K34" s="9"/>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3612,31 +3729,31 @@
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>583</v>
-      </c>
-      <c r="J35" s="7">
-        <v>1</v>
-      </c>
-      <c r="K35" s="7"/>
+      <c r="C35" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="J35" s="9">
+        <v>2</v>
+      </c>
+      <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -3644,159 +3761,159 @@
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J36" s="9">
-        <v>1</v>
-      </c>
-      <c r="K36" s="9"/>
-    </row>
-    <row r="37" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="J36" s="7">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>543</v>
+      <c r="C37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J37" s="7">
-        <v>1</v>
-      </c>
-      <c r="K37" s="7"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="9">
+        <v>1</v>
+      </c>
+      <c r="K37" s="9"/>
+    </row>
+    <row r="38" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>10</v>
+      <c r="C38" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J38" s="9">
-        <v>1</v>
-      </c>
-      <c r="K38" s="9"/>
-    </row>
-    <row r="39" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="7">
+        <v>1</v>
+      </c>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>543</v>
+      <c r="C39" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J39" s="7">
-        <v>1</v>
-      </c>
-      <c r="K39" s="7"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="9">
+        <v>1</v>
+      </c>
+      <c r="K39" s="9"/>
+    </row>
+    <row r="40" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="F40" s="9" t="s">
+      <c r="C40" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>544</v>
+      <c r="G40" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J40" s="9">
-        <v>5</v>
-      </c>
-      <c r="K40" s="9"/>
+      <c r="J40" s="7">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -3804,31 +3921,31 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J41" s="9">
         <v>5</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J41" s="7">
-        <v>5</v>
-      </c>
-      <c r="K41" s="7"/>
+      <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -3836,31 +3953,31 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>546</v>
+      <c r="C42" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>545</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J42" s="9">
-        <v>1</v>
-      </c>
-      <c r="K42" s="9"/>
+      <c r="J42" s="7">
+        <v>5</v>
+      </c>
+      <c r="K42" s="7"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -3868,31 +3985,31 @@
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="H43" s="7" t="s">
+      <c r="C43" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>546</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J43" s="7">
-        <v>1</v>
-      </c>
-      <c r="K43" s="7"/>
+      <c r="J43" s="9">
+        <v>1</v>
+      </c>
+      <c r="K43" s="9"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -3900,31 +4017,31 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="H44" s="9" t="s">
+      <c r="C44" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="H44" s="7" t="s">
         <v>546</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J44" s="9">
-        <v>1</v>
-      </c>
-      <c r="K44" s="9"/>
+      <c r="J44" s="7">
+        <v>1</v>
+      </c>
+      <c r="K44" s="7"/>
     </row>
     <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -3935,28 +4052,28 @@
       <c r="C45" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="H45" s="7" t="s">
+      <c r="D45" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>546</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J45" s="7">
-        <v>1</v>
-      </c>
-      <c r="K45" s="7"/>
+      <c r="J45" s="9">
+        <v>1</v>
+      </c>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
@@ -3967,28 +4084,28 @@
       <c r="C46" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>547</v>
+      <c r="D46" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J46" s="9">
-        <v>8</v>
-      </c>
-      <c r="K46" s="9"/>
+      <c r="J46" s="7">
+        <v>1</v>
+      </c>
+      <c r="K46" s="7"/>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
@@ -3996,95 +4113,95 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F47" s="7" t="s">
+      <c r="C47" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>548</v>
+      <c r="G47" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>547</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J47" s="7">
-        <v>6</v>
-      </c>
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J47" s="9">
+        <v>8</v>
+      </c>
+      <c r="K47" s="9"/>
+    </row>
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>549</v>
+      <c r="C48" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>548</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J48" s="9">
-        <v>4</v>
-      </c>
-      <c r="K48" s="9"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="7">
+        <v>6</v>
+      </c>
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="F49" s="7" t="s">
+      <c r="C49" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F49" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="G49" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>550</v>
+      <c r="G49" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>549</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J49" s="7">
+      <c r="J49" s="9">
         <v>4</v>
       </c>
-      <c r="K49" s="7"/>
+      <c r="K49" s="9"/>
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
@@ -4092,95 +4209,95 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J50" s="7">
         <v>4</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J50" s="9">
-        <v>8</v>
-      </c>
-      <c r="K50" s="9"/>
-    </row>
-    <row r="51" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>551</v>
+      <c r="D51" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J51" s="7">
+      <c r="J51" s="9">
         <v>8</v>
       </c>
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K51" s="9"/>
+    </row>
+    <row r="52" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>545</v>
+      <c r="C52" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>551</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J52" s="9">
-        <v>1</v>
-      </c>
-      <c r="K52" s="9"/>
+      <c r="J52" s="7">
+        <v>8</v>
+      </c>
+      <c r="K52" s="7"/>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -4188,31 +4305,31 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="H53" s="7" t="s">
+      <c r="C53" s="13" t="s">
         <v>10</v>
       </c>
+      <c r="D53" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>545</v>
+      </c>
       <c r="I53" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J53" s="7">
-        <v>1</v>
-      </c>
-      <c r="K53" s="7"/>
+      <c r="J53" s="9">
+        <v>1</v>
+      </c>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -4220,31 +4337,31 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="H54" s="9" t="s">
+      <c r="C54" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="H54" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I54" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J54" s="9">
-        <v>2</v>
-      </c>
-      <c r="K54" s="9"/>
+      <c r="J54" s="7">
+        <v>1</v>
+      </c>
+      <c r="K54" s="7"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
@@ -4252,33 +4369,33 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>552</v>
+      <c r="C55" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I55" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J55" s="7">
-        <v>1</v>
-      </c>
-      <c r="K55" s="7"/>
-    </row>
-    <row r="56" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J55" s="9">
+        <v>2</v>
+      </c>
+      <c r="K55" s="9"/>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f t="shared" si="1"/>
@@ -4287,60 +4404,60 @@
       <c r="C56" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>553</v>
+      <c r="D56" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="I56" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J56" s="9">
-        <v>6</v>
-      </c>
-      <c r="K56" s="9"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J56" s="7">
+        <v>1</v>
+      </c>
+      <c r="K56" s="7"/>
+    </row>
+    <row r="57" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>536</v>
+        <v>12</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>553</v>
       </c>
       <c r="I57" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J57" s="7">
-        <v>1</v>
-      </c>
-      <c r="K57" s="7"/>
+      <c r="J57" s="9">
+        <v>6</v>
+      </c>
+      <c r="K57" s="9"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
@@ -4348,31 +4465,31 @@
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F58" s="9" t="s">
+      <c r="C58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="G58" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="H58" s="9" t="s">
+      <c r="G58" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="H58" s="7" t="s">
         <v>536</v>
       </c>
       <c r="I58" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J58" s="9">
-        <v>4</v>
-      </c>
-      <c r="K58" s="9"/>
+      <c r="J58" s="7">
+        <v>1</v>
+      </c>
+      <c r="K58" s="7"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
@@ -4380,183 +4497,185 @@
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>241</v>
+      <c r="C59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>554</v>
+        <v>357</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>536</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J59" s="7">
-        <v>1</v>
-      </c>
-      <c r="K59" s="7"/>
-    </row>
-    <row r="60" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J59" s="9">
+        <v>4</v>
+      </c>
+      <c r="K59" s="9"/>
+    </row>
+    <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="11">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>242</v>
+      <c r="C60" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>241</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>555</v>
+      <c r="G60" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>554</v>
       </c>
       <c r="I60" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J60" s="9">
-        <v>1</v>
-      </c>
-      <c r="K60" s="9"/>
-    </row>
-    <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J60" s="7">
+        <v>1</v>
+      </c>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="11">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>243</v>
+      <c r="C61" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>242</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G61" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>556</v>
+      <c r="G61" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>555</v>
       </c>
       <c r="I61" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J61" s="7">
-        <v>1</v>
-      </c>
-      <c r="K61" s="7"/>
-    </row>
-    <row r="62" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J61" s="9">
+        <v>1</v>
+      </c>
+      <c r="K61" s="9"/>
+    </row>
+    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="I62" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J62" s="9">
-        <v>1</v>
-      </c>
-      <c r="K62" s="9"/>
-    </row>
-    <row r="63" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="J62" s="19">
+        <v>1</v>
+      </c>
+      <c r="K62" s="23" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>245</v>
+      <c r="C63" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>558</v>
+        <v>360</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>557</v>
       </c>
       <c r="I63" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J63" s="7">
-        <v>1</v>
-      </c>
-      <c r="K63" s="7"/>
-    </row>
-    <row r="64" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J63" s="9">
+        <v>1</v>
+      </c>
+      <c r="K63" s="9"/>
+    </row>
+    <row r="64" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>652</v>
+        <v>95</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>648</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I64" s="10" t="s">
         <v>650</v>
@@ -4572,52 +4691,52 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>260</v>
+      <c r="D65" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G65" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="H65" s="9" t="s">
+      <c r="G65" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H65" s="7" t="s">
         <v>559</v>
       </c>
       <c r="I65" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J65" s="9">
-        <v>1</v>
-      </c>
-      <c r="K65" s="9"/>
-    </row>
-    <row r="66" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J65" s="7">
+        <v>1</v>
+      </c>
+      <c r="K65" s="7"/>
+    </row>
+    <row r="66" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>96</v>
+        <v>651</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>648</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>559</v>
@@ -4626,41 +4745,41 @@
         <v>650</v>
       </c>
       <c r="J66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>557</v>
+      <c r="C67" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>559</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J67" s="7">
-        <v>6</v>
-      </c>
-      <c r="K67" s="7"/>
+      <c r="J67" s="9">
+        <v>2</v>
+      </c>
+      <c r="K67" s="9"/>
     </row>
     <row r="68" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -4668,95 +4787,95 @@
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>560</v>
+      <c r="C68" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>557</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J68" s="9">
-        <v>2</v>
-      </c>
-      <c r="K68" s="9"/>
-    </row>
-    <row r="69" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J68" s="7">
+        <v>6</v>
+      </c>
+      <c r="K68" s="7"/>
+    </row>
+    <row r="69" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>249</v>
+      <c r="C69" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G69" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>559</v>
+      <c r="G69" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>560</v>
       </c>
       <c r="I69" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J69" s="7">
-        <v>1</v>
-      </c>
-      <c r="K69" s="7"/>
-    </row>
-    <row r="70" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J69" s="9">
+        <v>2</v>
+      </c>
+      <c r="K69" s="9"/>
+    </row>
+    <row r="70" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="C70" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>250</v>
+      <c r="C70" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G70" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>555</v>
+      <c r="G70" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>559</v>
       </c>
       <c r="I70" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J70" s="9">
-        <v>2</v>
-      </c>
-      <c r="K70" s="9"/>
+      <c r="J70" s="7">
+        <v>1</v>
+      </c>
+      <c r="K70" s="7"/>
     </row>
     <row r="71" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
@@ -4764,95 +4883,95 @@
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>251</v>
+      <c r="D71" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G71" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="H71" s="7" t="s">
+      <c r="G71" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>555</v>
       </c>
       <c r="I71" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J71" s="7">
+      <c r="J71" s="9">
         <v>2</v>
       </c>
-      <c r="K71" s="7"/>
-    </row>
-    <row r="72" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K71" s="9"/>
+    </row>
+    <row r="72" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
-        <f t="shared" ref="B72:B135" si="2">ROW(B72) - ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>252</v>
+      <c r="C72" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G72" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>561</v>
+      <c r="G72" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="I72" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J72" s="9">
+      <c r="J72" s="7">
         <v>2</v>
       </c>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="73" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K72" s="7"/>
+    </row>
+    <row r="73" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B73:B136" si="2">ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>253</v>
+      <c r="C73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G73" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>555</v>
+      <c r="G73" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J73" s="7">
+      <c r="J73" s="9">
         <v>2</v>
       </c>
-      <c r="K73" s="7"/>
+      <c r="K73" s="9"/>
     </row>
     <row r="74" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -4860,31 +4979,31 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D74" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>254</v>
+      <c r="D74" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G74" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="H74" s="9" t="s">
+      <c r="G74" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H74" s="7" t="s">
         <v>555</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J74" s="9">
+      <c r="J74" s="7">
         <v>2</v>
       </c>
-      <c r="K74" s="9"/>
+      <c r="K74" s="7"/>
     </row>
     <row r="75" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
@@ -4892,31 +5011,31 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>255</v>
+      <c r="D75" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G75" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="H75" s="7" t="s">
+      <c r="G75" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>555</v>
       </c>
       <c r="I75" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J75" s="7">
+      <c r="J75" s="9">
         <v>2</v>
       </c>
-      <c r="K75" s="7"/>
+      <c r="K75" s="9"/>
     </row>
     <row r="76" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -4924,31 +5043,31 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>256</v>
+      <c r="D76" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G76" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H76" s="9" t="s">
+      <c r="G76" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H76" s="7" t="s">
         <v>555</v>
       </c>
       <c r="I76" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J76" s="9">
+      <c r="J76" s="7">
         <v>2</v>
       </c>
-      <c r="K76" s="9"/>
+      <c r="K76" s="7"/>
     </row>
     <row r="77" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
@@ -4956,31 +5075,31 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>257</v>
+      <c r="D77" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G77" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>560</v>
+      <c r="G77" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>555</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J77" s="7">
+      <c r="J77" s="9">
         <v>2</v>
       </c>
-      <c r="K77" s="7"/>
+      <c r="K77" s="9"/>
     </row>
     <row r="78" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -4988,31 +5107,31 @@
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>258</v>
+      <c r="C78" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G78" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>562</v>
+      <c r="G78" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J78" s="9">
-        <v>1</v>
-      </c>
-      <c r="K78" s="9"/>
+      <c r="J78" s="7">
+        <v>2</v>
+      </c>
+      <c r="K78" s="7"/>
     </row>
     <row r="79" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -5020,95 +5139,95 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C79" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>259</v>
+      <c r="C79" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G79" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>560</v>
+      <c r="G79" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>562</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J79" s="7">
-        <v>1</v>
-      </c>
-      <c r="K79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J79" s="9">
+        <v>1</v>
+      </c>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>262</v>
+      <c r="C80" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G80" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>547</v>
+      <c r="G80" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>605</v>
-      </c>
-      <c r="J80" s="9">
-        <v>1</v>
-      </c>
-      <c r="K80" s="9"/>
-    </row>
-    <row r="81" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J80" s="7">
+        <v>1</v>
+      </c>
+      <c r="K80" s="7"/>
+    </row>
+    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>263</v>
+      <c r="D81" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G81" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="J81" s="7">
-        <v>1</v>
-      </c>
-      <c r="K81" s="7"/>
+      <c r="G81" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="J81" s="9">
+        <v>1</v>
+      </c>
+      <c r="K81" s="9"/>
     </row>
     <row r="82" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
@@ -5116,31 +5235,31 @@
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>264</v>
+      <c r="C82" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J82" s="9">
-        <v>5</v>
-      </c>
-      <c r="K82" s="9"/>
+        <v>648</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="J82" s="7">
+        <v>1</v>
+      </c>
+      <c r="K82" s="7"/>
     </row>
     <row r="83" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
@@ -5148,31 +5267,31 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="F83" s="7" t="s">
+      <c r="D83" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F83" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="H83" s="7" t="s">
+      <c r="G83" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>564</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J83" s="7">
-        <v>1</v>
-      </c>
-      <c r="K83" s="7"/>
+      <c r="J83" s="9">
+        <v>5</v>
+      </c>
+      <c r="K83" s="9"/>
     </row>
     <row r="84" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -5180,31 +5299,31 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="F84" s="9" t="s">
+      <c r="D84" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="G84" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="H84" s="9" t="s">
+      <c r="G84" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="H84" s="7" t="s">
         <v>564</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J84" s="9">
-        <v>2</v>
-      </c>
-      <c r="K84" s="9"/>
+      <c r="J84" s="7">
+        <v>1</v>
+      </c>
+      <c r="K84" s="7"/>
     </row>
     <row r="85" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -5212,63 +5331,63 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C85" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>267</v>
+      <c r="C85" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>266</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>565</v>
+        <v>380</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>564</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J85" s="7">
-        <v>9</v>
-      </c>
-      <c r="K85" s="7"/>
-    </row>
-    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J85" s="9">
+        <v>2</v>
+      </c>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="86" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C86" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>268</v>
+      <c r="C86" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>10</v>
+        <v>648</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="I86" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J86" s="9">
-        <v>1</v>
-      </c>
-      <c r="K86" s="9"/>
+      <c r="J86" s="7">
+        <v>9</v>
+      </c>
+      <c r="K86" s="7"/>
     </row>
     <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
@@ -5276,63 +5395,63 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>548</v>
+      <c r="C87" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I87" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J87" s="7">
-        <v>1</v>
-      </c>
-      <c r="K87" s="7"/>
-    </row>
-    <row r="88" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J87" s="9">
+        <v>1</v>
+      </c>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C88" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>566</v>
+      <c r="C88" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>548</v>
       </c>
       <c r="I88" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J88" s="9">
-        <v>5</v>
-      </c>
-      <c r="K88" s="9"/>
+      <c r="J88" s="7">
+        <v>1</v>
+      </c>
+      <c r="K88" s="7"/>
     </row>
     <row r="89" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
@@ -5340,127 +5459,127 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="F89" s="7" t="s">
+      <c r="C89" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F89" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G89" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>567</v>
+      <c r="G89" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>566</v>
       </c>
       <c r="I89" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J89" s="7">
-        <v>4</v>
-      </c>
-      <c r="K89" s="7"/>
-    </row>
-    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J89" s="9">
+        <v>5</v>
+      </c>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>545</v>
+      <c r="C90" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="I90" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J90" s="9">
-        <v>1</v>
-      </c>
-      <c r="K90" s="9"/>
-    </row>
-    <row r="91" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J90" s="7">
+        <v>4</v>
+      </c>
+      <c r="K90" s="7"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C91" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>568</v>
+      <c r="C91" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="J91" s="7">
-        <v>6</v>
-      </c>
-      <c r="K91" s="7"/>
-    </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J91" s="9">
+        <v>1</v>
+      </c>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>29</v>
+      <c r="C92" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>655</v>
+        <v>121</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I92" s="8" t="s">
-        <v>607</v>
+        <v>568</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="J92" s="7">
-        <v>3</v>
-      </c>
-      <c r="K92" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="K92" s="7"/>
     </row>
     <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -5468,31 +5587,31 @@
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>122</v>
+        <v>655</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>386</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>535</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J93" s="7">
-        <v>1</v>
-      </c>
-      <c r="K93" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="K93" s="9"/>
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -5500,31 +5619,31 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D94" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="H94" s="9" t="s">
+      <c r="D94" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="H94" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I94" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="J94" s="9">
-        <v>1</v>
-      </c>
-      <c r="K94" s="9"/>
+      <c r="I94" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1</v>
+      </c>
+      <c r="K94" s="7"/>
     </row>
     <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
@@ -5533,25 +5652,25 @@
         <v>93</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>385</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>535</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J95" s="9">
         <v>1</v>
@@ -5564,31 +5683,31 @@
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="H96" s="7" t="s">
+      <c r="D96" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H96" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I96" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="J96" s="7">
-        <v>1</v>
-      </c>
-      <c r="K96" s="7"/>
+      <c r="I96" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="J96" s="9">
+        <v>1</v>
+      </c>
+      <c r="K96" s="9"/>
     </row>
     <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
@@ -5599,28 +5718,28 @@
       <c r="C97" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F97" s="9" t="s">
+      <c r="D97" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F97" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G97" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="H97" s="9" t="s">
+      <c r="G97" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="H97" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I97" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="J97" s="9">
-        <v>1</v>
-      </c>
-      <c r="K97" s="9"/>
+      <c r="I97" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="J97" s="7">
+        <v>1</v>
+      </c>
+      <c r="K97" s="7"/>
     </row>
     <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
@@ -5631,126 +5750,126 @@
       <c r="C98" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D98" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F98" s="7" t="s">
+      <c r="D98" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F98" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G98" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="H98" s="7" t="s">
+      <c r="G98" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="H98" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I98" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="J98" s="7">
-        <v>6</v>
-      </c>
-      <c r="K98" s="7"/>
-    </row>
-    <row r="99" spans="1:11" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I98" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="J98" s="9">
+        <v>1</v>
+      </c>
+      <c r="K98" s="9"/>
+    </row>
+    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D99" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F99" s="9" t="s">
+      <c r="D99" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F99" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G99" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="H99" s="9" t="s">
+      <c r="G99" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="H99" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I99" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="J99" s="9">
-        <v>172</v>
-      </c>
-      <c r="K99" s="9"/>
-    </row>
-    <row r="100" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I99" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="J99" s="7">
+        <v>6</v>
+      </c>
+      <c r="K99" s="7"/>
+    </row>
+    <row r="100" spans="1:11" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="C100" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F100" s="7" t="s">
+      <c r="C100" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="F100" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G100" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="H100" s="7" t="s">
+      <c r="G100" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="H100" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I100" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="J100" s="7">
-        <v>42</v>
-      </c>
-      <c r="K100" s="7"/>
-    </row>
-    <row r="101" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I100" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="J100" s="9">
+        <v>172</v>
+      </c>
+      <c r="K100" s="9"/>
+    </row>
+    <row r="101" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F101" s="9" t="s">
+      <c r="D101" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F101" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G101" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="H101" s="9" t="s">
+      <c r="G101" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="H101" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I101" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="J101" s="9">
-        <v>12</v>
-      </c>
-      <c r="K101" s="9"/>
-    </row>
-    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I101" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="J101" s="7">
+        <v>42</v>
+      </c>
+      <c r="K101" s="7"/>
+    </row>
+    <row r="102" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
         <f t="shared" si="2"/>
@@ -5759,28 +5878,28 @@
       <c r="C102" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="H102" s="7" t="s">
+      <c r="D102" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="H102" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I102" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="J102" s="7">
-        <v>4</v>
-      </c>
-      <c r="K102" s="7"/>
+      <c r="I102" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="J102" s="9">
+        <v>12</v>
+      </c>
+      <c r="K102" s="9"/>
     </row>
     <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -5791,30 +5910,28 @@
       <c r="C103" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D103" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="H103" s="14" t="s">
+      <c r="D103" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="H103" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I103" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="J103" s="14">
-        <v>3</v>
-      </c>
-      <c r="K103" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="I103" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="J103" s="7">
+        <v>4</v>
+      </c>
+      <c r="K103" s="7"/>
     </row>
     <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
@@ -5825,28 +5942,30 @@
       <c r="C104" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D104" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F104" s="7" t="s">
+      <c r="D104" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F104" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="G104" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="H104" s="7" t="s">
+      <c r="G104" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="H104" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="I104" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="J104" s="7">
-        <v>4</v>
-      </c>
-      <c r="K104" s="7"/>
+      <c r="I104" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="J104" s="14">
+        <v>3</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
@@ -5857,28 +5976,28 @@
       <c r="C105" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>487</v>
-      </c>
-      <c r="H105" s="9" t="s">
+      <c r="D105" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="H105" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I105" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="J105" s="9">
-        <v>1</v>
-      </c>
-      <c r="K105" s="9"/>
+      <c r="I105" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="J105" s="7">
+        <v>4</v>
+      </c>
+      <c r="K105" s="7"/>
     </row>
     <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
@@ -5889,30 +6008,30 @@
       <c r="C106" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="H106" s="7" t="s">
+      <c r="D106" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="H106" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I106" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="J106" s="7">
-        <v>3</v>
-      </c>
-      <c r="K106" s="7"/>
-    </row>
-    <row r="107" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I106" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="J106" s="9">
+        <v>1</v>
+      </c>
+      <c r="K106" s="9"/>
+    </row>
+    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
         <f t="shared" si="2"/>
@@ -5921,60 +6040,60 @@
       <c r="C107" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D107" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="F107" s="9" t="s">
+      <c r="D107" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F107" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G107" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="H107" s="9" t="s">
+      <c r="G107" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="H107" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I107" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="J107" s="9">
-        <v>16</v>
-      </c>
-      <c r="K107" s="9"/>
-    </row>
-    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I107" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="J107" s="7">
+        <v>3</v>
+      </c>
+      <c r="K107" s="7"/>
+    </row>
+    <row r="108" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D108" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F108" s="7" t="s">
+      <c r="D108" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F108" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G108" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="H108" s="7" t="s">
+      <c r="G108" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="H108" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I108" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="J108" s="7">
-        <v>1</v>
-      </c>
-      <c r="K108" s="7"/>
+      <c r="I108" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J108" s="9">
+        <v>16</v>
+      </c>
+      <c r="K108" s="9"/>
     </row>
     <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
@@ -5982,31 +6101,31 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D109" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="H109" s="9" t="s">
+      <c r="D109" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="H109" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I109" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="J109" s="9">
-        <v>1</v>
-      </c>
-      <c r="K109" s="9"/>
+      <c r="I109" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="J109" s="7">
+        <v>1</v>
+      </c>
+      <c r="K109" s="7"/>
     </row>
     <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
@@ -6014,31 +6133,31 @@
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D110" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F110" s="7" t="s">
+      <c r="D110" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F110" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="G110" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="H110" s="7" t="s">
+      <c r="G110" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="H110" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I110" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="J110" s="7">
-        <v>1</v>
-      </c>
-      <c r="K110" s="7"/>
+      <c r="I110" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J110" s="9">
+        <v>1</v>
+      </c>
+      <c r="K110" s="9"/>
     </row>
     <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
@@ -6046,31 +6165,31 @@
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D111" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G111" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="H111" s="9" t="s">
+      <c r="D111" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H111" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I111" s="10" t="s">
-        <v>626</v>
-      </c>
-      <c r="J111" s="9">
-        <v>2</v>
-      </c>
-      <c r="K111" s="9"/>
+      <c r="I111" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="J111" s="7">
+        <v>1</v>
+      </c>
+      <c r="K111" s="7"/>
     </row>
     <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
@@ -6078,95 +6197,95 @@
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D112" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="H112" s="7" t="s">
+      <c r="D112" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="H112" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I112" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="J112" s="7">
-        <v>6</v>
-      </c>
-      <c r="K112" s="7"/>
-    </row>
-    <row r="113" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I112" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="J112" s="9">
+        <v>2</v>
+      </c>
+      <c r="K112" s="9"/>
+    </row>
+    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D113" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="F113" s="9" t="s">
+      <c r="D113" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G113" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="H113" s="9" t="s">
+      <c r="G113" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="H113" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I113" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="J113" s="9">
-        <v>9</v>
-      </c>
-      <c r="K113" s="9"/>
-    </row>
-    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I113" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="J113" s="7">
+        <v>6</v>
+      </c>
+      <c r="K113" s="7"/>
+    </row>
+    <row r="114" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G114" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="H114" s="7" t="s">
+      <c r="D114" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="H114" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I114" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="J114" s="7">
-        <v>2</v>
-      </c>
-      <c r="K114" s="7"/>
+      <c r="I114" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="J114" s="9">
+        <v>9</v>
+      </c>
+      <c r="K114" s="9"/>
     </row>
     <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
@@ -6174,31 +6293,31 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D115" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="H115" s="9" t="s">
+      <c r="D115" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="H115" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I115" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="J115" s="9">
-        <v>4</v>
-      </c>
-      <c r="K115" s="9"/>
+      <c r="I115" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="J115" s="7">
+        <v>2</v>
+      </c>
+      <c r="K115" s="7"/>
     </row>
     <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
@@ -6206,31 +6325,31 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="H116" s="7" t="s">
+      <c r="D116" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="H116" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I116" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="J116" s="7">
-        <v>1</v>
-      </c>
-      <c r="K116" s="7"/>
+      <c r="I116" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="J116" s="9">
+        <v>4</v>
+      </c>
+      <c r="K116" s="9"/>
     </row>
     <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
@@ -6238,33 +6357,31 @@
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D117" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E117" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="F117" s="14" t="s">
+      <c r="D117" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="F117" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G117" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="H117" s="14" t="s">
+      <c r="G117" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="H117" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I117" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="J117" s="14">
-        <v>1</v>
-      </c>
-      <c r="K117" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="I117" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="J117" s="7">
+        <v>1</v>
+      </c>
+      <c r="K117" s="7"/>
     </row>
     <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
@@ -6275,92 +6392,94 @@
       <c r="C118" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D118" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="F118" s="9" t="s">
+      <c r="D118" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F118" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="G118" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="H118" s="9" t="s">
+      <c r="G118" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="H118" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="I118" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="J118" s="9">
-        <v>4</v>
-      </c>
-      <c r="K118" s="9"/>
-    </row>
-    <row r="119" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I118" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="J118" s="14">
+        <v>1</v>
+      </c>
+      <c r="K118" s="16" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="11">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D119" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="F119" s="7" t="s">
+      <c r="D119" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F119" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G119" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="I119" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="J119" s="7">
-        <v>8</v>
-      </c>
-      <c r="K119" s="7"/>
-    </row>
-    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G119" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="J119" s="9">
+        <v>4</v>
+      </c>
+      <c r="K119" s="9"/>
+    </row>
+    <row r="120" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="11">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="C120" s="13" t="s">
+      <c r="C120" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D120" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I120" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="J120" s="9">
-        <v>4</v>
-      </c>
-      <c r="K120" s="9"/>
+      <c r="D120" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="J120" s="7">
+        <v>8</v>
+      </c>
+      <c r="K120" s="7"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
@@ -6368,31 +6487,31 @@
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D121" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="H121" s="7" t="s">
+      <c r="D121" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I121" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="J121" s="7">
-        <v>6</v>
-      </c>
-      <c r="K121" s="7"/>
+      <c r="I121" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="J121" s="9">
+        <v>4</v>
+      </c>
+      <c r="K121" s="9"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
@@ -6400,33 +6519,31 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D122" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="E122" s="15" t="s">
+      <c r="D122" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E122" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="F122" s="14" t="s">
+      <c r="F122" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="G122" s="15" t="s">
+      <c r="G122" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="H122" s="14" t="s">
+      <c r="H122" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I122" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="J122" s="14">
-        <v>2</v>
-      </c>
-      <c r="K122" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="I122" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="J122" s="7">
+        <v>6</v>
+      </c>
+      <c r="K122" s="7"/>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
@@ -6434,31 +6551,33 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="G123" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="H123" s="7" t="s">
+      <c r="D123" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E123" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="G123" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="H123" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="I123" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="J123" s="7">
-        <v>1</v>
-      </c>
-      <c r="K123" s="7"/>
+      <c r="I123" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="J123" s="14">
+        <v>2</v>
+      </c>
+      <c r="K123" s="16" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
@@ -6466,31 +6585,31 @@
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="C124" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D124" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G124" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="H124" s="9" t="s">
+      <c r="C124" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H124" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I124" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="J124" s="9">
-        <v>1</v>
-      </c>
-      <c r="K124" s="9"/>
+      <c r="I124" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="J124" s="7">
+        <v>1</v>
+      </c>
+      <c r="K124" s="7"/>
     </row>
     <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
@@ -6498,31 +6617,31 @@
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>656</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F125" s="7" t="s">
+      <c r="C125" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F125" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G125" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="H125" s="7" t="s">
+      <c r="G125" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="H125" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I125" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="J125" s="7">
-        <v>6</v>
-      </c>
-      <c r="K125" s="7"/>
+      <c r="I125" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="J125" s="9">
+        <v>1</v>
+      </c>
+      <c r="K125" s="9"/>
     </row>
     <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
@@ -6530,31 +6649,31 @@
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="H126" s="9" t="s">
+      <c r="D126" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="H126" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I126" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="J126" s="9">
-        <v>1</v>
-      </c>
-      <c r="K126" s="9"/>
+      <c r="I126" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="J126" s="7">
+        <v>6</v>
+      </c>
+      <c r="K126" s="7"/>
     </row>
     <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
@@ -6562,31 +6681,31 @@
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D127" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="F127" s="7" t="s">
+      <c r="D127" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F127" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="G127" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="H127" s="7" t="s">
+      <c r="G127" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="H127" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I127" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="J127" s="7">
-        <v>1</v>
-      </c>
-      <c r="K127" s="7"/>
+      <c r="I127" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="J127" s="9">
+        <v>1</v>
+      </c>
+      <c r="K127" s="9"/>
     </row>
     <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
@@ -6594,31 +6713,31 @@
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="C128" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="F128" s="9" t="s">
+      <c r="C128" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F128" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="G128" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="H128" s="9" t="s">
+      <c r="G128" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="H128" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I128" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="J128" s="9">
-        <v>1</v>
-      </c>
-      <c r="K128" s="9"/>
+      <c r="I128" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="J128" s="7">
+        <v>1</v>
+      </c>
+      <c r="K128" s="7"/>
     </row>
     <row r="129" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
@@ -6626,31 +6745,31 @@
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="H129" s="7" t="s">
+      <c r="C129" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I129" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="J129" s="7">
-        <v>1</v>
-      </c>
-      <c r="K129" s="7"/>
+      <c r="I129" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="J129" s="9">
+        <v>1</v>
+      </c>
+      <c r="K129" s="9"/>
     </row>
     <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
@@ -6658,31 +6777,31 @@
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
-      <c r="C130" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="F130" s="9" t="s">
+      <c r="C130" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F130" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G130" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="H130" s="9" t="s">
+      <c r="G130" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="H130" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="I130" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="J130" s="9">
-        <v>1</v>
-      </c>
-      <c r="K130" s="9"/>
+      <c r="I130" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="J130" s="7">
+        <v>1</v>
+      </c>
+      <c r="K130" s="7"/>
     </row>
     <row r="131" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
@@ -6691,28 +6810,28 @@
         <v>129</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>386</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H131" s="9" t="s">
         <v>535</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" s="9"/>
     </row>
@@ -6722,191 +6841,191 @@
         <f t="shared" si="2"/>
         <v>130</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>311</v>
+      <c r="C132" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J132" s="7">
-        <v>7</v>
-      </c>
-      <c r="K132" s="7"/>
-    </row>
-    <row r="133" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="J132" s="9">
+        <v>2</v>
+      </c>
+      <c r="K132" s="9"/>
+    </row>
+    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="11">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
-      <c r="C133" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>312</v>
+      <c r="C133" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G133" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>571</v>
+      <c r="G133" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>570</v>
       </c>
       <c r="I133" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J133" s="9">
-        <v>1</v>
-      </c>
-      <c r="K133" s="9"/>
-    </row>
-    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J133" s="7">
+        <v>7</v>
+      </c>
+      <c r="K133" s="7"/>
+    </row>
+    <row r="134" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="11">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="C134" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>313</v>
+      <c r="C134" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>312</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G134" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>572</v>
+      <c r="G134" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>571</v>
       </c>
       <c r="I134" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J134" s="7">
-        <v>1</v>
-      </c>
-      <c r="K134" s="7"/>
-    </row>
-    <row r="135" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J134" s="9">
+        <v>1</v>
+      </c>
+      <c r="K134" s="9"/>
+    </row>
+    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="11">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="C135" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>314</v>
+      <c r="C135" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>573</v>
+        <v>648</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>572</v>
       </c>
       <c r="I135" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J135" s="9">
-        <v>1</v>
-      </c>
-      <c r="K135" s="9"/>
-    </row>
-    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J135" s="7">
+        <v>1</v>
+      </c>
+      <c r="K135" s="7"/>
+    </row>
+    <row r="136" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="11">
-        <f t="shared" ref="B136:B156" si="3">ROW(B136) - ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D136" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="H136" s="7" t="s">
+      <c r="D136" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="H136" s="9" t="s">
         <v>573</v>
       </c>
       <c r="I136" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J136" s="7">
-        <v>1</v>
-      </c>
-      <c r="K136" s="7"/>
+      <c r="J136" s="9">
+        <v>1</v>
+      </c>
+      <c r="K136" s="9"/>
     </row>
     <row r="137" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="B137:B158" si="3">ROW(B137) - ROW($B$2)</f>
         <v>135</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D137" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>546</v>
+      <c r="D137" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>573</v>
       </c>
       <c r="I137" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J137" s="9">
-        <v>1</v>
-      </c>
-      <c r="K137" s="9"/>
+      <c r="J137" s="7">
+        <v>1</v>
+      </c>
+      <c r="K137" s="7"/>
     </row>
     <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
@@ -6914,31 +7033,31 @@
         <f t="shared" si="3"/>
         <v>136</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="H138" s="7" t="s">
+      <c r="D138" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="H138" s="9" t="s">
         <v>546</v>
       </c>
       <c r="I138" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J138" s="7">
-        <v>1</v>
-      </c>
-      <c r="K138" s="7"/>
+      <c r="J138" s="9">
+        <v>1</v>
+      </c>
+      <c r="K138" s="9"/>
     </row>
     <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
@@ -6946,31 +7065,31 @@
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D139" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>574</v>
+      <c r="D139" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="I139" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J139" s="9">
-        <v>1</v>
-      </c>
-      <c r="K139" s="9"/>
+      <c r="J139" s="7">
+        <v>1</v>
+      </c>
+      <c r="K139" s="7"/>
     </row>
     <row r="140" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
@@ -6978,63 +7097,63 @@
         <f t="shared" si="3"/>
         <v>138</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D140" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>546</v>
+      <c r="D140" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>574</v>
       </c>
       <c r="I140" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J140" s="7">
-        <v>1</v>
-      </c>
-      <c r="K140" s="7"/>
-    </row>
-    <row r="141" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J140" s="9">
+        <v>1</v>
+      </c>
+      <c r="K140" s="9"/>
+    </row>
+    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="11">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
-      <c r="C141" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G141" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>548</v>
+      <c r="C141" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J141" s="9">
-        <v>2</v>
-      </c>
-      <c r="K141" s="9"/>
+      <c r="J141" s="7">
+        <v>1</v>
+      </c>
+      <c r="K141" s="7"/>
     </row>
     <row r="142" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
@@ -7042,63 +7161,63 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="C142" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>575</v>
+      <c r="C142" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="I142" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J142" s="7">
-        <v>1</v>
-      </c>
-      <c r="K142" s="7"/>
-    </row>
-    <row r="143" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J142" s="9">
+        <v>2</v>
+      </c>
+      <c r="K142" s="9"/>
+    </row>
+    <row r="143" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="11">
         <f t="shared" si="3"/>
         <v>141</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D143" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>573</v>
+      <c r="D143" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>575</v>
       </c>
       <c r="I143" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J143" s="9">
-        <v>3</v>
-      </c>
-      <c r="K143" s="9"/>
+      <c r="J143" s="7">
+        <v>1</v>
+      </c>
+      <c r="K143" s="7"/>
     </row>
     <row r="144" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
@@ -7106,31 +7225,31 @@
         <f t="shared" si="3"/>
         <v>142</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D144" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="H144" s="7" t="s">
+      <c r="D144" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="H144" s="9" t="s">
         <v>573</v>
       </c>
       <c r="I144" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J144" s="7">
-        <v>2</v>
-      </c>
-      <c r="K144" s="7"/>
+      <c r="J144" s="9">
+        <v>3</v>
+      </c>
+      <c r="K144" s="9"/>
     </row>
     <row r="145" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
@@ -7138,31 +7257,31 @@
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C145" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D145" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="F145" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="H145" s="9" t="s">
+      <c r="D145" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="H145" s="7" t="s">
         <v>573</v>
       </c>
       <c r="I145" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J145" s="9">
-        <v>3</v>
-      </c>
-      <c r="K145" s="9"/>
+      <c r="J145" s="7">
+        <v>2</v>
+      </c>
+      <c r="K145" s="7"/>
     </row>
     <row r="146" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
@@ -7170,31 +7289,31 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D146" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>574</v>
+      <c r="D146" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I146" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J146" s="7">
-        <v>1</v>
-      </c>
-      <c r="K146" s="7"/>
+      <c r="J146" s="9">
+        <v>3</v>
+      </c>
+      <c r="K146" s="9"/>
     </row>
     <row r="147" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
@@ -7205,30 +7324,30 @@
       <c r="C147" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>545</v>
+      <c r="D147" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>574</v>
       </c>
       <c r="I147" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J147" s="9">
-        <v>1</v>
-      </c>
-      <c r="K147" s="9"/>
-    </row>
-    <row r="148" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J147" s="7">
+        <v>1</v>
+      </c>
+      <c r="K147" s="7"/>
+    </row>
+    <row r="148" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="11">
         <f t="shared" si="3"/>
@@ -7237,60 +7356,60 @@
       <c r="C148" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D148" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>326</v>
+      <c r="D148" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G148" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>576</v>
+      <c r="G148" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="I148" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J148" s="7">
-        <v>8</v>
-      </c>
-      <c r="K148" s="7"/>
-    </row>
-    <row r="149" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J148" s="9">
+        <v>1</v>
+      </c>
+      <c r="K148" s="9"/>
+    </row>
+    <row r="149" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="11">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C149" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D149" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>327</v>
+      <c r="D149" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>573</v>
+        <v>648</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>576</v>
       </c>
       <c r="I149" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J149" s="9">
-        <v>1</v>
-      </c>
-      <c r="K149" s="9"/>
+      <c r="J149" s="7">
+        <v>8</v>
+      </c>
+      <c r="K149" s="7"/>
     </row>
     <row r="150" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
@@ -7298,31 +7417,31 @@
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
-      <c r="C150" s="12" t="s">
+      <c r="C150" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="H150" s="7" t="s">
+      <c r="D150" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="H150" s="9" t="s">
         <v>573</v>
       </c>
       <c r="I150" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J150" s="7">
-        <v>1</v>
-      </c>
-      <c r="K150" s="7"/>
+      <c r="J150" s="9">
+        <v>1</v>
+      </c>
+      <c r="K150" s="9"/>
     </row>
     <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
@@ -7330,31 +7449,31 @@
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
-      <c r="C151" s="13" t="s">
+      <c r="C151" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D151" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="H151" s="9" t="s">
+      <c r="D151" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="H151" s="7" t="s">
         <v>573</v>
       </c>
       <c r="I151" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J151" s="9">
-        <v>1</v>
-      </c>
-      <c r="K151" s="9"/>
+      <c r="J151" s="7">
+        <v>1</v>
+      </c>
+      <c r="K151" s="7"/>
     </row>
     <row r="152" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
@@ -7362,31 +7481,31 @@
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="C152" s="12" t="s">
+      <c r="C152" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H152" s="7" t="s">
+      <c r="D152" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H152" s="9" t="s">
         <v>573</v>
       </c>
       <c r="I152" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J152" s="7">
-        <v>1</v>
-      </c>
-      <c r="K152" s="7"/>
+      <c r="J152" s="9">
+        <v>1</v>
+      </c>
+      <c r="K152" s="9"/>
     </row>
     <row r="153" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
@@ -7394,31 +7513,31 @@
         <f t="shared" si="3"/>
         <v>151</v>
       </c>
-      <c r="C153" s="13" t="s">
+      <c r="C153" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E153" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F153" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="G153" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="H153" s="9" t="s">
+      <c r="D153" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="H153" s="7" t="s">
         <v>573</v>
       </c>
       <c r="I153" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J153" s="9">
-        <v>1</v>
-      </c>
-      <c r="K153" s="9"/>
+      <c r="J153" s="7">
+        <v>1</v>
+      </c>
+      <c r="K153" s="7"/>
     </row>
     <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
@@ -7426,31 +7545,31 @@
         <f t="shared" si="3"/>
         <v>152</v>
       </c>
-      <c r="C154" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>332</v>
+      <c r="C154" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>577</v>
+        <v>407</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I154" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="J154" s="7">
-        <v>2</v>
-      </c>
-      <c r="K154" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J154" s="9">
+        <v>1</v>
+      </c>
+      <c r="K154" s="9"/>
     </row>
     <row r="155" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
@@ -7461,30 +7580,30 @@
       <c r="C155" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D155" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>333</v>
+      <c r="D155" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G155" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="I155" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="J155" s="9">
-        <v>1</v>
-      </c>
-      <c r="K155" s="9"/>
-    </row>
-    <row r="156" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G155" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="J155" s="7">
+        <v>2</v>
+      </c>
+      <c r="K155" s="7"/>
+    </row>
+    <row r="156" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B156" s="11">
         <f t="shared" si="3"/>
         <v>154</v>
@@ -7492,34 +7611,294 @@
       <c r="C156" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="D156" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="I156" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="J156" s="9">
+        <v>1</v>
+      </c>
+      <c r="K156" s="9"/>
+    </row>
+    <row r="157" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B157" s="11">
+        <f t="shared" si="3"/>
+        <v>155</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D157" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E156" s="8" t="s">
+      <c r="E157" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="F156" s="7" t="s">
+      <c r="F157" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="G156" s="8" t="s">
+      <c r="G157" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="H156" s="7" t="s">
+      <c r="H157" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="I156" s="8" t="s">
+      <c r="I157" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="J156" s="7">
-        <v>1</v>
-      </c>
-      <c r="K156" s="7"/>
+      <c r="J157" s="7">
+        <v>1</v>
+      </c>
+      <c r="K157" s="7"/>
+    </row>
+    <row r="158" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="11">
+        <f t="shared" si="3"/>
+        <v>156</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J158" s="9">
+        <v>1</v>
+      </c>
+      <c r="K158" s="9"/>
+    </row>
+    <row r="159" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="11">
+        <f>ROW(B159) - ROW($B$2)</f>
+        <v>157</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J159" s="7">
+        <v>6</v>
+      </c>
+      <c r="K159" s="7"/>
+    </row>
+    <row r="160" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="11">
+        <f t="shared" ref="B160:B162" si="4">ROW(B160) - ROW($B$2)</f>
+        <v>158</v>
+      </c>
+      <c r="C160" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="I160" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J160" s="9">
+        <v>1</v>
+      </c>
+      <c r="K160" s="24" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B161" s="11">
+        <f t="shared" si="4"/>
+        <v>159</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="J161" s="7">
+        <v>4</v>
+      </c>
+      <c r="K161" s="25" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B162" s="11">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="C162" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="J162" s="7"/>
+      <c r="K162" s="23" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="11">
+        <f>ROW(B163) - ROW($B$2)</f>
+        <v>161</v>
+      </c>
+      <c r="C163" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="J163" s="7">
+        <v>1</v>
+      </c>
+      <c r="K163" s="23" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B164" s="11">
+        <f>ROW(B164) - ROW($B$2)</f>
+        <v>162</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="K164" s="23" t="s">
+        <v>680</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K160" r:id="rId1"/>
+    <hyperlink ref="K161" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
+++ b/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="677">
   <si>
     <t>#</t>
   </si>
@@ -300,9 +300,6 @@
     <t>J2</t>
   </si>
   <si>
-    <t>J3</t>
-  </si>
-  <si>
     <t>J4</t>
   </si>
   <si>
@@ -750,9 +747,6 @@
     <t>1x3P 18A -40℃~+105℃ 250V Orange 12~30 Direct Insert 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw Terminal Blocks ROHS</t>
   </si>
   <si>
-    <t>CABLE ADAPTER 6 POS</t>
-  </si>
-  <si>
     <t>Gold 250V 3A Straight Square Pins 2.5mm 3P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x3P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
@@ -1413,9 +1407,6 @@
     <t>BLM18PG221SN1D</t>
   </si>
   <si>
-    <t>TC2030-IDC</t>
-  </si>
-  <si>
     <t>X6511WV-03H-C60D30</t>
   </si>
   <si>
@@ -1687,9 +1678,6 @@
   </si>
   <si>
     <t>DORABO</t>
-  </si>
-  <si>
-    <t>Tag-Connect</t>
   </si>
   <si>
     <t>XKB</t>
@@ -2068,7 +2056,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2131,13 +2119,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2273,9 +2254,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2324,29 +2305,17 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2636,7 +2605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2662,9 +2631,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2678,25 +2647,25 @@
         <v>36</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>643</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2712,19 +2681,19 @@
         <v>37</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="J3" s="7">
         <v>1</v>
@@ -2744,19 +2713,19 @@
         <v>38</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -2776,19 +2745,19 @@
         <v>39</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -2808,19 +2777,19 @@
         <v>40</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J6" s="9">
         <v>9</v>
@@ -2840,19 +2809,19 @@
         <v>41</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J7" s="7">
         <v>4</v>
@@ -2862,7 +2831,7 @@
     <row r="8" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B72" si="1">ROW(B8) - ROW($B$2)</f>
+        <f t="shared" ref="B8:B71" si="1">ROW(B8) - ROW($B$2)</f>
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -2872,19 +2841,19 @@
         <v>42</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J8" s="9">
         <v>13</v>
@@ -2904,19 +2873,19 @@
         <v>43</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
@@ -2936,19 +2905,19 @@
         <v>44</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="J10" s="9">
         <v>4</v>
@@ -2968,19 +2937,19 @@
         <v>45</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J11" s="7">
         <v>3</v>
@@ -3000,19 +2969,19 @@
         <v>46</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -3032,19 +3001,19 @@
         <v>47</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -3064,19 +3033,19 @@
         <v>48</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="J14" s="9">
         <v>5</v>
@@ -3093,22 +3062,22 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J15" s="7">
         <v>62</v>
@@ -3125,22 +3094,22 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J16" s="9">
         <v>4</v>
@@ -3160,19 +3129,19 @@
         <v>49</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J17" s="7">
         <v>6</v>
@@ -3192,19 +3161,19 @@
         <v>50</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -3224,19 +3193,19 @@
         <v>51</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="J19" s="7">
         <v>2</v>
@@ -3253,22 +3222,22 @@
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -3288,19 +3257,19 @@
         <v>52</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -3320,19 +3289,19 @@
         <v>53</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="J22" s="9">
         <v>8</v>
@@ -3352,19 +3321,19 @@
         <v>54</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -3384,19 +3353,19 @@
         <v>55</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="J24" s="7">
         <v>2</v>
@@ -3416,19 +3385,19 @@
         <v>56</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="J25" s="9">
         <v>1</v>
@@ -3448,19 +3417,19 @@
         <v>57</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="J26" s="7">
         <v>1</v>
@@ -3480,19 +3449,19 @@
         <v>58</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="J27" s="9">
         <v>1</v>
@@ -3512,19 +3481,19 @@
         <v>59</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J28" s="7">
         <v>1</v>
@@ -3544,19 +3513,19 @@
         <v>60</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="J29" s="9">
         <v>1</v>
@@ -3576,19 +3545,19 @@
         <v>61</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="J30" s="7">
         <v>1</v>
@@ -3608,19 +3577,19 @@
         <v>62</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="J31" s="9">
         <v>6</v>
@@ -3640,19 +3609,19 @@
         <v>63</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J32" s="7">
         <v>1</v>
@@ -3672,19 +3641,19 @@
         <v>64</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="J33" s="9">
         <v>3</v>
@@ -3704,19 +3673,19 @@
         <v>65</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="J34" s="7">
         <v>2</v>
@@ -3736,19 +3705,19 @@
         <v>66</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J35" s="9">
         <v>2</v>
@@ -3768,19 +3737,19 @@
         <v>67</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J36" s="7">
         <v>1</v>
@@ -3800,19 +3769,19 @@
         <v>68</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J37" s="9">
         <v>1</v>
@@ -3832,19 +3801,19 @@
         <v>69</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J38" s="7">
         <v>1</v>
@@ -3864,19 +3833,19 @@
         <v>70</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J39" s="9">
         <v>1</v>
@@ -3896,19 +3865,19 @@
         <v>71</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J40" s="7">
         <v>1</v>
@@ -3928,19 +3897,19 @@
         <v>72</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J41" s="9">
         <v>5</v>
@@ -3960,19 +3929,19 @@
         <v>73</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J42" s="7">
         <v>5</v>
@@ -3992,19 +3961,19 @@
         <v>74</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J43" s="9">
         <v>1</v>
@@ -4024,19 +3993,19 @@
         <v>75</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J44" s="7">
         <v>1</v>
@@ -4056,19 +4025,19 @@
         <v>76</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J45" s="9">
         <v>1</v>
@@ -4088,19 +4057,19 @@
         <v>77</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J46" s="7">
         <v>1</v>
@@ -4120,19 +4089,19 @@
         <v>78</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J47" s="9">
         <v>8</v>
@@ -4152,19 +4121,19 @@
         <v>79</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J48" s="7">
         <v>6</v>
@@ -4184,19 +4153,19 @@
         <v>80</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J49" s="9">
         <v>4</v>
@@ -4216,19 +4185,19 @@
         <v>81</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J50" s="7">
         <v>4</v>
@@ -4248,19 +4217,19 @@
         <v>82</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J51" s="9">
         <v>8</v>
@@ -4280,19 +4249,19 @@
         <v>83</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J52" s="7">
         <v>8</v>
@@ -4312,19 +4281,19 @@
         <v>84</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J53" s="9">
         <v>1</v>
@@ -4344,19 +4313,19 @@
         <v>85</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J54" s="7">
         <v>1</v>
@@ -4376,19 +4345,19 @@
         <v>86</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H55" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J55" s="9">
         <v>2</v>
@@ -4408,19 +4377,19 @@
         <v>87</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J56" s="7">
         <v>1</v>
@@ -4440,19 +4409,19 @@
         <v>88</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J57" s="9">
         <v>6</v>
@@ -4472,19 +4441,19 @@
         <v>89</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J58" s="7">
         <v>1</v>
@@ -4504,19 +4473,19 @@
         <v>90</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J59" s="9">
         <v>4</v>
@@ -4536,19 +4505,19 @@
         <v>91</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J60" s="7">
         <v>1</v>
@@ -4568,117 +4537,115 @@
         <v>92</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J61" s="9">
         <v>1</v>
       </c>
       <c r="K61" s="9"/>
     </row>
-    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="D62" s="19" t="s">
+      <c r="C62" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E62" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="F62" s="21" t="s">
-        <v>648</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="I62" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="J62" s="19">
-        <v>1</v>
-      </c>
-      <c r="K62" s="23" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E62" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J62" s="9">
+        <v>1</v>
+      </c>
+      <c r="K62" s="9"/>
+    </row>
+    <row r="63" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D63" s="9" t="s">
+      <c r="C63" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E63" s="10" t="s">
-        <v>244</v>
+      <c r="E63" s="8" t="s">
+        <v>243</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>557</v>
+        <v>644</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>554</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J63" s="9">
-        <v>1</v>
-      </c>
-      <c r="K63" s="9"/>
-    </row>
-    <row r="64" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J63" s="7">
+        <v>1</v>
+      </c>
+      <c r="K63" s="7"/>
+    </row>
+    <row r="64" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>95</v>
+        <v>648</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J64" s="7">
         <v>1</v>
@@ -4691,95 +4658,95 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>261</v>
+      <c r="D65" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>559</v>
+        <v>644</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>555</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J65" s="7">
-        <v>1</v>
-      </c>
-      <c r="K65" s="7"/>
-    </row>
-    <row r="66" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J65" s="9">
+        <v>1</v>
+      </c>
+      <c r="K65" s="9"/>
+    </row>
+    <row r="66" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>651</v>
+        <v>95</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J66" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C67" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D67" s="9" t="s">
+      <c r="C67" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>559</v>
+      <c r="E67" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>553</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J67" s="9">
-        <v>2</v>
-      </c>
-      <c r="K67" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J67" s="7">
+        <v>6</v>
+      </c>
+      <c r="K67" s="7"/>
     </row>
     <row r="68" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -4787,95 +4754,95 @@
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="7" t="s">
+      <c r="C68" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>557</v>
+      <c r="E68" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>556</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J68" s="7">
-        <v>6</v>
-      </c>
-      <c r="K68" s="7"/>
-    </row>
-    <row r="69" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J68" s="9">
+        <v>2</v>
+      </c>
+      <c r="K68" s="9"/>
+    </row>
+    <row r="69" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D69" s="9" t="s">
+      <c r="C69" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E69" s="10" t="s">
-        <v>248</v>
+      <c r="E69" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>560</v>
+        <v>644</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J69" s="9">
-        <v>2</v>
-      </c>
-      <c r="K69" s="9"/>
-    </row>
-    <row r="70" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J69" s="7">
+        <v>1</v>
+      </c>
+      <c r="K69" s="7"/>
+    </row>
+    <row r="70" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="C70" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70" s="7" t="s">
+      <c r="C70" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>249</v>
+      <c r="E70" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>559</v>
+        <v>644</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>552</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J70" s="7">
-        <v>1</v>
-      </c>
-      <c r="K70" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J70" s="9">
+        <v>2</v>
+      </c>
+      <c r="K70" s="9"/>
     </row>
     <row r="71" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
@@ -4883,95 +4850,95 @@
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>250</v>
+      <c r="E71" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>555</v>
+        <v>644</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J71" s="9">
+        <v>646</v>
+      </c>
+      <c r="J71" s="7">
         <v>2</v>
       </c>
-      <c r="K71" s="9"/>
-    </row>
-    <row r="72" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K71" s="7"/>
+    </row>
+    <row r="72" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B72:B135" si="2">ROW(B72) - ROW($B$2)</f>
         <v>70</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" s="7" t="s">
+      <c r="C72" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E72" s="8" t="s">
-        <v>251</v>
+      <c r="E72" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>555</v>
+        <v>644</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>557</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J72" s="7">
+        <v>646</v>
+      </c>
+      <c r="J72" s="9">
         <v>2</v>
       </c>
-      <c r="K72" s="7"/>
-    </row>
-    <row r="73" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f t="shared" ref="B73:B136" si="2">ROW(B73) - ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="9" t="s">
+      <c r="C73" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E73" s="10" t="s">
-        <v>252</v>
+      <c r="E73" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>561</v>
+        <v>644</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J73" s="9">
+        <v>646</v>
+      </c>
+      <c r="J73" s="7">
         <v>2</v>
       </c>
-      <c r="K73" s="9"/>
+      <c r="K73" s="7"/>
     </row>
     <row r="74" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -4979,31 +4946,31 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E74" s="8" t="s">
-        <v>253</v>
+      <c r="E74" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>555</v>
+        <v>644</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>552</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J74" s="7">
+        <v>646</v>
+      </c>
+      <c r="J74" s="9">
         <v>2</v>
       </c>
-      <c r="K74" s="7"/>
+      <c r="K74" s="9"/>
     </row>
     <row r="75" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
@@ -5011,31 +4978,31 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="D75" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E75" s="10" t="s">
-        <v>254</v>
+      <c r="E75" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>555</v>
+        <v>644</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J75" s="9">
+        <v>646</v>
+      </c>
+      <c r="J75" s="7">
         <v>2</v>
       </c>
-      <c r="K75" s="9"/>
+      <c r="K75" s="7"/>
     </row>
     <row r="76" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -5043,31 +5010,31 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E76" s="8" t="s">
-        <v>255</v>
+      <c r="E76" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>555</v>
+        <v>644</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>552</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J76" s="7">
+        <v>646</v>
+      </c>
+      <c r="J76" s="9">
         <v>2</v>
       </c>
-      <c r="K76" s="7"/>
+      <c r="K76" s="9"/>
     </row>
     <row r="77" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
@@ -5075,31 +5042,31 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D77" s="9" t="s">
+      <c r="D77" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E77" s="10" t="s">
-        <v>256</v>
+      <c r="E77" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>555</v>
+        <v>644</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>556</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J77" s="9">
+        <v>646</v>
+      </c>
+      <c r="J77" s="7">
         <v>2</v>
       </c>
-      <c r="K77" s="9"/>
+      <c r="K77" s="7"/>
     </row>
     <row r="78" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -5107,31 +5074,31 @@
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" s="7" t="s">
+      <c r="C78" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E78" s="8" t="s">
-        <v>257</v>
+      <c r="E78" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>560</v>
+        <v>644</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>558</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J78" s="7">
-        <v>2</v>
-      </c>
-      <c r="K78" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J78" s="9">
+        <v>1</v>
+      </c>
+      <c r="K78" s="9"/>
     </row>
     <row r="79" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -5139,95 +5106,95 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D79" s="9" t="s">
+      <c r="C79" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="E79" s="10" t="s">
-        <v>258</v>
+      <c r="E79" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>562</v>
+        <v>644</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>556</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J79" s="9">
-        <v>1</v>
-      </c>
-      <c r="K79" s="9"/>
-    </row>
-    <row r="80" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J79" s="7">
+        <v>1</v>
+      </c>
+      <c r="K79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C80" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="7" t="s">
+      <c r="C80" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E80" s="8" t="s">
-        <v>259</v>
+      <c r="E80" s="10" t="s">
+        <v>260</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>560</v>
+        <v>644</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>544</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J80" s="7">
-        <v>1</v>
-      </c>
-      <c r="K80" s="7"/>
-    </row>
-    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+      <c r="J80" s="9">
+        <v>1</v>
+      </c>
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E81" s="10" t="s">
-        <v>262</v>
+      <c r="E81" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="I81" s="10" t="s">
-        <v>605</v>
-      </c>
-      <c r="J81" s="9">
-        <v>1</v>
-      </c>
-      <c r="K81" s="9"/>
+        <v>644</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="J81" s="7">
+        <v>1</v>
+      </c>
+      <c r="K81" s="7"/>
     </row>
     <row r="82" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
@@ -5235,31 +5202,31 @@
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="7" t="s">
+      <c r="C82" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E82" s="8" t="s">
-        <v>263</v>
+      <c r="E82" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="J82" s="7">
-        <v>1</v>
-      </c>
-      <c r="K82" s="7"/>
+        <v>378</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J82" s="9">
+        <v>5</v>
+      </c>
+      <c r="K82" s="9"/>
     </row>
     <row r="83" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
@@ -5267,31 +5234,31 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E83" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>564</v>
+      <c r="E83" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J83" s="9">
-        <v>5</v>
-      </c>
-      <c r="K83" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J83" s="7">
+        <v>1</v>
+      </c>
+      <c r="K83" s="7"/>
     </row>
     <row r="84" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -5299,31 +5266,31 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E84" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>564</v>
+      <c r="E84" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>560</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J84" s="7">
-        <v>1</v>
-      </c>
-      <c r="K84" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J84" s="9">
+        <v>2</v>
+      </c>
+      <c r="K84" s="9"/>
     </row>
     <row r="85" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -5331,63 +5298,63 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C85" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D85" s="9" t="s">
+      <c r="C85" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E85" s="10" t="s">
-        <v>266</v>
+      <c r="E85" s="8" t="s">
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>564</v>
+        <v>644</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>561</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J85" s="9">
-        <v>2</v>
-      </c>
-      <c r="K85" s="9"/>
-    </row>
-    <row r="86" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J85" s="7">
+        <v>9</v>
+      </c>
+      <c r="K85" s="7"/>
+    </row>
+    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C86" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D86" s="7" t="s">
+      <c r="C86" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E86" s="8" t="s">
-        <v>267</v>
+      <c r="E86" s="10" t="s">
+        <v>266</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>565</v>
+        <v>380</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J86" s="7">
-        <v>9</v>
-      </c>
-      <c r="K86" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J86" s="9">
+        <v>1</v>
+      </c>
+      <c r="K86" s="9"/>
     </row>
     <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
@@ -5395,63 +5362,63 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C87" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D87" s="9" t="s">
+      <c r="C87" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E87" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>10</v>
+      <c r="E87" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>545</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J87" s="9">
-        <v>1</v>
-      </c>
-      <c r="K87" s="9"/>
-    </row>
-    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J87" s="7">
+        <v>1</v>
+      </c>
+      <c r="K87" s="7"/>
+    </row>
+    <row r="88" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D88" s="7" t="s">
+      <c r="C88" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E88" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>548</v>
+      <c r="E88" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>562</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J88" s="7">
-        <v>1</v>
-      </c>
-      <c r="K88" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J88" s="9">
+        <v>5</v>
+      </c>
+      <c r="K88" s="9"/>
     </row>
     <row r="89" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
@@ -5459,127 +5426,127 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C89" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D89" s="9" t="s">
+      <c r="C89" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E89" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>566</v>
+      <c r="E89" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>563</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J89" s="9">
-        <v>5</v>
-      </c>
-      <c r="K89" s="9"/>
-    </row>
-    <row r="90" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J89" s="7">
+        <v>4</v>
+      </c>
+      <c r="K89" s="7"/>
+    </row>
+    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D90" s="7" t="s">
+      <c r="C90" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E90" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>567</v>
+      <c r="E90" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>542</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J90" s="7">
-        <v>4</v>
-      </c>
-      <c r="K90" s="7"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J90" s="9">
+        <v>1</v>
+      </c>
+      <c r="K90" s="9"/>
+    </row>
+    <row r="91" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C91" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D91" s="9" t="s">
+      <c r="C91" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D91" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E91" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>545</v>
+      <c r="E91" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>564</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J91" s="9">
-        <v>1</v>
-      </c>
-      <c r="K91" s="9"/>
-    </row>
-    <row r="92" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J91" s="7">
+        <v>6</v>
+      </c>
+      <c r="K91" s="7"/>
+    </row>
+    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>26</v>
+      <c r="C92" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>121</v>
+        <v>651</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>474</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="I92" s="10" t="s">
-        <v>650</v>
+        <v>532</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>603</v>
       </c>
       <c r="J92" s="7">
-        <v>6</v>
-      </c>
-      <c r="K92" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="K92" s="9"/>
     </row>
     <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -5587,31 +5554,31 @@
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>655</v>
+        <v>121</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="J93" s="7">
-        <v>3</v>
-      </c>
-      <c r="K93" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="K93" s="7"/>
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -5619,31 +5586,31 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="D94" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E94" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I94" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="J94" s="7">
-        <v>1</v>
-      </c>
-      <c r="K94" s="7"/>
+      <c r="E94" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="J94" s="9">
+        <v>1</v>
+      </c>
+      <c r="K94" s="9"/>
     </row>
     <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
@@ -5652,7 +5619,7 @@
         <v>93</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>123</v>
@@ -5661,16 +5628,16 @@
         <v>275</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J95" s="9">
         <v>1</v>
@@ -5683,31 +5650,31 @@
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D96" s="9" t="s">
+      <c r="D96" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E96" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I96" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="J96" s="9">
-        <v>1</v>
-      </c>
-      <c r="K96" s="9"/>
+      <c r="E96" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="J96" s="7">
+        <v>1</v>
+      </c>
+      <c r="K96" s="7"/>
     </row>
     <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
@@ -5718,28 +5685,28 @@
       <c r="C97" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E97" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="J97" s="7">
-        <v>1</v>
-      </c>
-      <c r="K97" s="7"/>
+      <c r="E97" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="J97" s="9">
+        <v>1</v>
+      </c>
+      <c r="K97" s="9"/>
     </row>
     <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
@@ -5750,126 +5717,126 @@
       <c r="C98" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D98" s="9" t="s">
+      <c r="D98" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E98" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I98" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="J98" s="9">
-        <v>1</v>
-      </c>
-      <c r="K98" s="9"/>
-    </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E98" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="J98" s="7">
+        <v>6</v>
+      </c>
+      <c r="K98" s="7"/>
+    </row>
+    <row r="99" spans="1:11" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D99" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E99" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="J99" s="7">
-        <v>6</v>
-      </c>
-      <c r="K99" s="7"/>
-    </row>
-    <row r="100" spans="1:11" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="J99" s="9">
+        <v>172</v>
+      </c>
+      <c r="K99" s="9"/>
+    </row>
+    <row r="100" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="C100" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="H100" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I100" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="J100" s="9">
-        <v>172</v>
-      </c>
-      <c r="K100" s="9"/>
-    </row>
-    <row r="101" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C100" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="J100" s="7">
+        <v>42</v>
+      </c>
+      <c r="K100" s="7"/>
+    </row>
+    <row r="101" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D101" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I101" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="J101" s="7">
-        <v>42</v>
-      </c>
-      <c r="K101" s="7"/>
-    </row>
-    <row r="102" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D101" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="J101" s="9">
+        <v>12</v>
+      </c>
+      <c r="K101" s="9"/>
+    </row>
+    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
         <f t="shared" si="2"/>
@@ -5878,28 +5845,28 @@
       <c r="C102" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D102" s="9" t="s">
+      <c r="D102" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E102" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I102" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="J102" s="9">
-        <v>12</v>
-      </c>
-      <c r="K102" s="9"/>
+      <c r="E102" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="J102" s="7">
+        <v>4</v>
+      </c>
+      <c r="K102" s="7"/>
     </row>
     <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -5910,28 +5877,30 @@
       <c r="C103" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="E103" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I103" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="J103" s="7">
-        <v>4</v>
-      </c>
-      <c r="K103" s="7"/>
+      <c r="E103" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="I103" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="J103" s="14">
+        <v>3</v>
+      </c>
+      <c r="K103" s="16" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
@@ -5942,30 +5911,28 @@
       <c r="C104" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D104" s="14" t="s">
+      <c r="D104" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E104" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="F104" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="G104" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="H104" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="I104" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="J104" s="14">
-        <v>3</v>
-      </c>
-      <c r="K104" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="E104" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="J104" s="7">
+        <v>4</v>
+      </c>
+      <c r="K104" s="7"/>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
@@ -5976,28 +5943,28 @@
       <c r="C105" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E105" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F105" s="7" t="s">
+      <c r="E105" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F105" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G105" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="J105" s="7">
-        <v>4</v>
-      </c>
-      <c r="K105" s="7"/>
+      <c r="G105" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="J105" s="9">
+        <v>1</v>
+      </c>
+      <c r="K105" s="9"/>
     </row>
     <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
@@ -6008,30 +5975,30 @@
       <c r="C106" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D106" s="9" t="s">
+      <c r="D106" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E106" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>487</v>
-      </c>
-      <c r="H106" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I106" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="J106" s="9">
-        <v>1</v>
-      </c>
-      <c r="K106" s="9"/>
-    </row>
-    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E106" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="J106" s="7">
+        <v>3</v>
+      </c>
+      <c r="K106" s="7"/>
+    </row>
+    <row r="107" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
         <f t="shared" si="2"/>
@@ -6040,60 +6007,60 @@
       <c r="C107" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E107" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="J107" s="7">
-        <v>3</v>
-      </c>
-      <c r="K107" s="7"/>
-    </row>
-    <row r="108" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="J107" s="9">
+        <v>16</v>
+      </c>
+      <c r="K107" s="9"/>
+    </row>
+    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D108" s="9" t="s">
+      <c r="D108" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E108" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G108" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="H108" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I108" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="J108" s="9">
-        <v>16</v>
-      </c>
-      <c r="K108" s="9"/>
+      <c r="E108" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="J108" s="7">
+        <v>1</v>
+      </c>
+      <c r="K108" s="7"/>
     </row>
     <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
@@ -6101,31 +6068,31 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E109" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F109" s="7" t="s">
+      <c r="E109" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F109" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G109" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="J109" s="7">
-        <v>1</v>
-      </c>
-      <c r="K109" s="7"/>
+      <c r="G109" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="J109" s="9">
+        <v>1</v>
+      </c>
+      <c r="K109" s="9"/>
     </row>
     <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
@@ -6133,31 +6100,31 @@
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="C110" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D110" s="9" t="s">
+      <c r="D110" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E110" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I110" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="J110" s="9">
-        <v>1</v>
-      </c>
-      <c r="K110" s="9"/>
+      <c r="E110" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="J110" s="7">
+        <v>1</v>
+      </c>
+      <c r="K110" s="7"/>
     </row>
     <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
@@ -6165,31 +6132,31 @@
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
-      <c r="C111" s="12" t="s">
+      <c r="C111" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E111" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I111" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="J111" s="7">
-        <v>1</v>
-      </c>
-      <c r="K111" s="7"/>
+      <c r="E111" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J111" s="9">
+        <v>2</v>
+      </c>
+      <c r="K111" s="9"/>
     </row>
     <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
@@ -6197,95 +6164,95 @@
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C112" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D112" s="9" t="s">
+      <c r="D112" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E112" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="F112" s="9" t="s">
+      <c r="E112" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F112" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G112" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="H112" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I112" s="10" t="s">
-        <v>626</v>
-      </c>
-      <c r="J112" s="9">
-        <v>2</v>
-      </c>
-      <c r="K112" s="9"/>
-    </row>
-    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G112" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="J112" s="7">
+        <v>6</v>
+      </c>
+      <c r="K112" s="7"/>
+    </row>
+    <row r="113" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E113" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I113" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="J113" s="7">
-        <v>6</v>
-      </c>
-      <c r="K113" s="7"/>
-    </row>
-    <row r="114" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E113" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I113" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="J113" s="9">
+        <v>9</v>
+      </c>
+      <c r="K113" s="9"/>
+    </row>
+    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D114" s="9" t="s">
+      <c r="D114" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E114" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G114" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="H114" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I114" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="J114" s="9">
-        <v>9</v>
-      </c>
-      <c r="K114" s="9"/>
+      <c r="E114" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="J114" s="7">
+        <v>2</v>
+      </c>
+      <c r="K114" s="7"/>
     </row>
     <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
@@ -6293,31 +6260,31 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="C115" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E115" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="F115" s="7" t="s">
+      <c r="E115" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F115" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G115" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I115" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="J115" s="7">
-        <v>2</v>
-      </c>
-      <c r="K115" s="7"/>
+      <c r="G115" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J115" s="9">
+        <v>4</v>
+      </c>
+      <c r="K115" s="9"/>
     </row>
     <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
@@ -6325,31 +6292,31 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D116" s="9" t="s">
+      <c r="D116" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E116" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="H116" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="J116" s="9">
-        <v>4</v>
-      </c>
-      <c r="K116" s="9"/>
+      <c r="E116" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="J116" s="7">
+        <v>1</v>
+      </c>
+      <c r="K116" s="7"/>
     </row>
     <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
@@ -6357,31 +6324,33 @@
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="E117" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G117" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="J117" s="7">
-        <v>1</v>
-      </c>
-      <c r="K117" s="7"/>
+      <c r="E117" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="G117" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="H117" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="I117" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="J117" s="14">
+        <v>1</v>
+      </c>
+      <c r="K117" s="16" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
@@ -6392,94 +6361,92 @@
       <c r="C118" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D118" s="14" t="s">
+      <c r="D118" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E118" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="F118" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="G118" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="H118" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="I118" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="J118" s="14">
-        <v>1</v>
-      </c>
-      <c r="K118" s="16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E118" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="J118" s="9">
+        <v>4</v>
+      </c>
+      <c r="K118" s="9"/>
+    </row>
+    <row r="119" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="11">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D119" s="9" t="s">
+      <c r="D119" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E119" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I119" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="J119" s="9">
-        <v>4</v>
-      </c>
-      <c r="K119" s="9"/>
-    </row>
-    <row r="120" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E119" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="J119" s="7">
+        <v>8</v>
+      </c>
+      <c r="K119" s="7"/>
+    </row>
+    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="11">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="D120" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E120" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="F120" s="7" t="s">
+      <c r="E120" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F120" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G120" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="I120" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="J120" s="7">
-        <v>8</v>
-      </c>
-      <c r="K120" s="7"/>
+      <c r="G120" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I120" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="J120" s="9">
+        <v>4</v>
+      </c>
+      <c r="K120" s="9"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
@@ -6487,31 +6454,31 @@
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="D121" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E121" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I121" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="J121" s="9">
-        <v>4</v>
-      </c>
-      <c r="K121" s="9"/>
+      <c r="E121" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="J121" s="7">
+        <v>6</v>
+      </c>
+      <c r="K121" s="7"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
@@ -6519,31 +6486,33 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D122" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E122" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I122" s="8" t="s">
+      <c r="E122" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="F122" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="G122" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="H122" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="I122" s="15" t="s">
         <v>614</v>
       </c>
-      <c r="J122" s="7">
-        <v>6</v>
-      </c>
-      <c r="K122" s="7"/>
+      <c r="J122" s="14">
+        <v>2</v>
+      </c>
+      <c r="K122" s="16" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
@@ -6551,33 +6520,31 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D123" s="14" t="s">
+      <c r="D123" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E123" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="F123" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="G123" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="H123" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="I123" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="J123" s="14">
-        <v>2</v>
-      </c>
-      <c r="K123" s="16" t="s">
-        <v>645</v>
-      </c>
+      <c r="E123" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="J123" s="7">
+        <v>1</v>
+      </c>
+      <c r="K123" s="7"/>
     </row>
     <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
@@ -6585,31 +6552,31 @@
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="C124" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D124" s="7" t="s">
+      <c r="C124" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D124" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E124" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I124" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="J124" s="7">
-        <v>1</v>
-      </c>
-      <c r="K124" s="7"/>
+      <c r="E124" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I124" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="J124" s="9">
+        <v>1</v>
+      </c>
+      <c r="K124" s="9"/>
     </row>
     <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
@@ -6617,31 +6584,31 @@
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
-      <c r="C125" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I125" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="J125" s="9">
-        <v>1</v>
-      </c>
-      <c r="K125" s="9"/>
+      <c r="C125" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="J125" s="7">
+        <v>6</v>
+      </c>
+      <c r="K125" s="7"/>
     </row>
     <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
@@ -6649,31 +6616,31 @@
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="C126" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D126" s="7" t="s">
-        <v>656</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I126" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="J126" s="7">
-        <v>6</v>
-      </c>
-      <c r="K126" s="7"/>
+      <c r="D126" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I126" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="J126" s="9">
+        <v>1</v>
+      </c>
+      <c r="K126" s="9"/>
     </row>
     <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
@@ -6681,31 +6648,31 @@
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="D127" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E127" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="G127" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I127" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="J127" s="9">
-        <v>1</v>
-      </c>
-      <c r="K127" s="9"/>
+      <c r="E127" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="J127" s="7">
+        <v>1</v>
+      </c>
+      <c r="K127" s="7"/>
     </row>
     <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
@@ -6713,31 +6680,31 @@
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D128" s="7" t="s">
+      <c r="C128" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E128" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="G128" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I128" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="J128" s="7">
-        <v>1</v>
-      </c>
-      <c r="K128" s="7"/>
+      <c r="E128" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I128" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="J128" s="9">
+        <v>1</v>
+      </c>
+      <c r="K128" s="9"/>
     </row>
     <row r="129" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
@@ -6745,31 +6712,31 @@
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="C129" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" s="9" t="s">
+      <c r="C129" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E129" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="G129" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I129" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="J129" s="9">
-        <v>1</v>
-      </c>
-      <c r="K129" s="9"/>
+      <c r="E129" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="J129" s="7">
+        <v>1</v>
+      </c>
+      <c r="K129" s="7"/>
     </row>
     <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
@@ -6777,31 +6744,31 @@
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D130" s="7" t="s">
+      <c r="C130" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E130" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="I130" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="J130" s="7">
-        <v>1</v>
-      </c>
-      <c r="K130" s="7"/>
+      <c r="E130" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="J130" s="9">
+        <v>1</v>
+      </c>
+      <c r="K130" s="9"/>
     </row>
     <row r="131" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
@@ -6810,7 +6777,7 @@
         <v>129</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>157</v>
@@ -6819,19 +6786,19 @@
         <v>308</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J131" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" s="9"/>
     </row>
@@ -6841,191 +6808,191 @@
         <f t="shared" si="2"/>
         <v>130</v>
       </c>
-      <c r="C132" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D132" s="9" t="s">
+      <c r="C132" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D132" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E132" s="10" t="s">
-        <v>310</v>
+      <c r="E132" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="I132" s="10" t="s">
-        <v>640</v>
-      </c>
-      <c r="J132" s="9">
-        <v>2</v>
-      </c>
-      <c r="K132" s="9"/>
-    </row>
-    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="J132" s="7">
+        <v>7</v>
+      </c>
+      <c r="K132" s="7"/>
+    </row>
+    <row r="133" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="11">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
-      <c r="C133" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D133" s="7" t="s">
+      <c r="C133" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D133" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E133" s="8" t="s">
-        <v>311</v>
+      <c r="E133" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>570</v>
+        <v>644</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J133" s="7">
-        <v>7</v>
-      </c>
-      <c r="K133" s="7"/>
-    </row>
-    <row r="134" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J133" s="9">
+        <v>1</v>
+      </c>
+      <c r="K133" s="9"/>
+    </row>
+    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="11">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="C134" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D134" s="9" t="s">
+      <c r="C134" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D134" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E134" s="10" t="s">
-        <v>312</v>
+      <c r="E134" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>571</v>
+        <v>644</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>568</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J134" s="9">
-        <v>1</v>
-      </c>
-      <c r="K134" s="9"/>
-    </row>
-    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J134" s="7">
+        <v>1</v>
+      </c>
+      <c r="K134" s="7"/>
+    </row>
+    <row r="135" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="11">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="C135" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D135" s="7" t="s">
+      <c r="C135" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E135" s="8" t="s">
-        <v>313</v>
+      <c r="E135" s="10" t="s">
+        <v>312</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>572</v>
+        <v>345</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J135" s="7">
-        <v>1</v>
-      </c>
-      <c r="K135" s="7"/>
-    </row>
-    <row r="136" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J135" s="9">
+        <v>1</v>
+      </c>
+      <c r="K135" s="9"/>
+    </row>
+    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B136:B157" si="3">ROW(B136) - ROW($B$2)</f>
         <v>134</v>
       </c>
-      <c r="C136" s="13" t="s">
+      <c r="C136" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D136" s="9" t="s">
+      <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E136" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F136" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>573</v>
+      <c r="E136" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J136" s="9">
-        <v>1</v>
-      </c>
-      <c r="K136" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J136" s="7">
+        <v>1</v>
+      </c>
+      <c r="K136" s="7"/>
     </row>
     <row r="137" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="11">
-        <f t="shared" ref="B137:B158" si="3">ROW(B137) - ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>135</v>
       </c>
-      <c r="C137" s="12" t="s">
+      <c r="C137" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D137" s="7" t="s">
+      <c r="D137" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E137" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="G137" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>573</v>
+      <c r="E137" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>543</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J137" s="7">
-        <v>1</v>
-      </c>
-      <c r="K137" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J137" s="9">
+        <v>1</v>
+      </c>
+      <c r="K137" s="9"/>
     </row>
     <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
@@ -7033,31 +7000,31 @@
         <f t="shared" si="3"/>
         <v>136</v>
       </c>
-      <c r="C138" s="13" t="s">
+      <c r="C138" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="9" t="s">
+      <c r="D138" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E138" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="F138" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="G138" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="H138" s="9" t="s">
-        <v>546</v>
+      <c r="E138" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J138" s="9">
-        <v>1</v>
-      </c>
-      <c r="K138" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J138" s="7">
+        <v>1</v>
+      </c>
+      <c r="K138" s="7"/>
     </row>
     <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
@@ -7065,31 +7032,31 @@
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="D139" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E139" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>546</v>
+      <c r="E139" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J139" s="7">
-        <v>1</v>
-      </c>
-      <c r="K139" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J139" s="9">
+        <v>1</v>
+      </c>
+      <c r="K139" s="9"/>
     </row>
     <row r="140" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
@@ -7097,63 +7064,63 @@
         <f t="shared" si="3"/>
         <v>138</v>
       </c>
-      <c r="C140" s="13" t="s">
+      <c r="C140" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D140" s="9" t="s">
+      <c r="D140" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E140" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="G140" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="H140" s="9" t="s">
-        <v>574</v>
+      <c r="E140" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J140" s="9">
-        <v>1</v>
-      </c>
-      <c r="K140" s="9"/>
-    </row>
-    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J140" s="7">
+        <v>1</v>
+      </c>
+      <c r="K140" s="7"/>
+    </row>
+    <row r="141" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="11">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
-      <c r="C141" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D141" s="7" t="s">
+      <c r="C141" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E141" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>546</v>
+      <c r="E141" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J141" s="7">
-        <v>1</v>
-      </c>
-      <c r="K141" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J141" s="9">
+        <v>2</v>
+      </c>
+      <c r="K141" s="9"/>
     </row>
     <row r="142" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
@@ -7161,63 +7128,63 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="C142" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D142" s="9" t="s">
+      <c r="C142" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E142" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G142" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>548</v>
+      <c r="E142" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>571</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J142" s="9">
-        <v>2</v>
-      </c>
-      <c r="K142" s="9"/>
-    </row>
-    <row r="143" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J142" s="7">
+        <v>1</v>
+      </c>
+      <c r="K142" s="7"/>
+    </row>
+    <row r="143" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="11">
         <f t="shared" si="3"/>
         <v>141</v>
       </c>
-      <c r="C143" s="12" t="s">
+      <c r="C143" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="D143" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E143" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>575</v>
+      <c r="E143" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J143" s="7">
-        <v>1</v>
-      </c>
-      <c r="K143" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J143" s="9">
+        <v>3</v>
+      </c>
+      <c r="K143" s="9"/>
     </row>
     <row r="144" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
@@ -7225,31 +7192,31 @@
         <f t="shared" si="3"/>
         <v>142</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C144" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D144" s="9" t="s">
+      <c r="D144" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E144" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="G144" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="H144" s="9" t="s">
-        <v>573</v>
+      <c r="E144" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J144" s="9">
-        <v>3</v>
-      </c>
-      <c r="K144" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J144" s="7">
+        <v>2</v>
+      </c>
+      <c r="K144" s="7"/>
     </row>
     <row r="145" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
@@ -7257,31 +7224,31 @@
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
-      <c r="C145" s="12" t="s">
+      <c r="C145" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="D145" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E145" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F145" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="G145" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>573</v>
+      <c r="E145" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J145" s="7">
-        <v>2</v>
-      </c>
-      <c r="K145" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J145" s="9">
+        <v>3</v>
+      </c>
+      <c r="K145" s="9"/>
     </row>
     <row r="146" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
@@ -7289,31 +7256,31 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="C146" s="13" t="s">
+      <c r="C146" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D146" s="9" t="s">
+      <c r="D146" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="E146" s="10" t="s">
+      <c r="E146" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="F146" s="9" t="s">
+      <c r="F146" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="G146" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>573</v>
+      <c r="G146" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>570</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J146" s="9">
-        <v>3</v>
-      </c>
-      <c r="K146" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J146" s="7">
+        <v>1</v>
+      </c>
+      <c r="K146" s="7"/>
     </row>
     <row r="147" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
@@ -7324,30 +7291,30 @@
       <c r="C147" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="D147" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E147" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="G147" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>574</v>
+      <c r="E147" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>542</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J147" s="7">
-        <v>1</v>
-      </c>
-      <c r="K147" s="7"/>
-    </row>
-    <row r="148" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J147" s="9">
+        <v>1</v>
+      </c>
+      <c r="K147" s="9"/>
+    </row>
+    <row r="148" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="11">
         <f t="shared" si="3"/>
@@ -7356,60 +7323,60 @@
       <c r="C148" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D148" s="9" t="s">
+      <c r="D148" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E148" s="10" t="s">
-        <v>325</v>
+      <c r="E148" s="8" t="s">
+        <v>324</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G148" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="H148" s="9" t="s">
-        <v>545</v>
+        <v>644</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>572</v>
       </c>
       <c r="I148" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J148" s="9">
-        <v>1</v>
-      </c>
-      <c r="K148" s="9"/>
-    </row>
-    <row r="149" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J148" s="7">
+        <v>8</v>
+      </c>
+      <c r="K148" s="7"/>
+    </row>
+    <row r="149" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="11">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
-      <c r="C149" s="12" t="s">
+      <c r="C149" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="D149" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E149" s="8" t="s">
-        <v>326</v>
+      <c r="E149" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>576</v>
+        <v>401</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J149" s="7">
-        <v>8</v>
-      </c>
-      <c r="K149" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J149" s="9">
+        <v>1</v>
+      </c>
+      <c r="K149" s="9"/>
     </row>
     <row r="150" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
@@ -7417,31 +7384,31 @@
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
-      <c r="C150" s="13" t="s">
+      <c r="C150" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D150" s="9" t="s">
+      <c r="D150" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="E150" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="F150" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="G150" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="H150" s="9" t="s">
-        <v>573</v>
+      <c r="E150" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J150" s="9">
-        <v>1</v>
-      </c>
-      <c r="K150" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J150" s="7">
+        <v>1</v>
+      </c>
+      <c r="K150" s="7"/>
     </row>
     <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
@@ -7449,31 +7416,31 @@
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
-      <c r="C151" s="12" t="s">
+      <c r="C151" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="D151" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E151" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>573</v>
+      <c r="E151" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J151" s="7">
-        <v>1</v>
-      </c>
-      <c r="K151" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J151" s="9">
+        <v>1</v>
+      </c>
+      <c r="K151" s="9"/>
     </row>
     <row r="152" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
@@ -7481,31 +7448,31 @@
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="C152" s="13" t="s">
+      <c r="C152" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="9" t="s">
+      <c r="D152" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E152" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F152" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="G152" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="H152" s="9" t="s">
-        <v>573</v>
+      <c r="E152" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="I152" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J152" s="9">
-        <v>1</v>
-      </c>
-      <c r="K152" s="9"/>
+        <v>646</v>
+      </c>
+      <c r="J152" s="7">
+        <v>1</v>
+      </c>
+      <c r="K152" s="7"/>
     </row>
     <row r="153" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
@@ -7513,31 +7480,31 @@
         <f t="shared" si="3"/>
         <v>151</v>
       </c>
-      <c r="C153" s="12" t="s">
+      <c r="C153" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="D153" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="F153" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>573</v>
+      <c r="E153" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G153" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I153" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J153" s="7">
-        <v>1</v>
-      </c>
-      <c r="K153" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J153" s="9">
+        <v>1</v>
+      </c>
+      <c r="K153" s="9"/>
     </row>
     <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
@@ -7545,34 +7512,33 @@
         <f t="shared" si="3"/>
         <v>152</v>
       </c>
-      <c r="C154" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D154" s="9" t="s">
+      <c r="C154" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D154" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E154" s="10" t="s">
-        <v>331</v>
+      <c r="E154" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="G154" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="H154" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H154" s="7" t="s">
         <v>573</v>
       </c>
       <c r="I154" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J154" s="9">
-        <v>1</v>
-      </c>
-      <c r="K154" s="9"/>
+        <v>637</v>
+      </c>
+      <c r="J154" s="7">
+        <v>2</v>
+      </c>
+      <c r="K154" s="7"/>
     </row>
     <row r="155" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="1"/>
       <c r="B155" s="11">
         <f t="shared" si="3"/>
         <v>153</v>
@@ -7580,30 +7546,30 @@
       <c r="C155" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="D155" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E155" s="8" t="s">
-        <v>332</v>
+      <c r="E155" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="I155" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="J155" s="7">
-        <v>2</v>
-      </c>
-      <c r="K155" s="7"/>
-    </row>
-    <row r="156" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="I155" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="J155" s="9">
+        <v>1</v>
+      </c>
+      <c r="K155" s="9"/>
+    </row>
+    <row r="156" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B156" s="11">
         <f t="shared" si="3"/>
         <v>154</v>
@@ -7611,283 +7577,252 @@
       <c r="C156" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D156" s="9" t="s">
+      <c r="D156" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E156" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="F156" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G156" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="H156" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="I156" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="J156" s="9">
-        <v>1</v>
-      </c>
-      <c r="K156" s="9"/>
+      <c r="E156" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="I156" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J156" s="7">
+        <v>1</v>
+      </c>
+      <c r="K156" s="7"/>
     </row>
     <row r="157" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="11">
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-      <c r="C157" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F157" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="I157" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="J157" s="7">
-        <v>1</v>
-      </c>
-      <c r="K157" s="7"/>
+      <c r="C157" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G157" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="H157" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="I157" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J157" s="9">
+        <v>1</v>
+      </c>
+      <c r="K157" s="9"/>
     </row>
     <row r="158" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B158" s="11">
-        <f t="shared" si="3"/>
+        <f>ROW(B158) - ROW($B$2)</f>
         <v>156</v>
       </c>
       <c r="C158" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G158" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="D158" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="F158" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G158" s="10" t="s">
+      <c r="H158" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J158" s="7">
+        <v>6</v>
+      </c>
+      <c r="K158" s="7"/>
+    </row>
+    <row r="159" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="11">
+        <f t="shared" ref="B159:B161" si="4">ROW(B159) - ROW($B$2)</f>
+        <v>157</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G159" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J159" s="9">
+        <v>1</v>
+      </c>
+      <c r="K159" s="19" t="s">
         <v>669</v>
       </c>
-      <c r="H158" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="I158" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J158" s="9">
-        <v>1</v>
-      </c>
-      <c r="K158" s="9"/>
-    </row>
-    <row r="159" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B159" s="11">
-        <f>ROW(B159) - ROW($B$2)</f>
-        <v>157</v>
-      </c>
-      <c r="C159" s="13" t="s">
-        <v>661</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>663</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G159" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="I159" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J159" s="7">
-        <v>6</v>
-      </c>
-      <c r="K159" s="7"/>
     </row>
     <row r="160" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B160" s="11">
-        <f t="shared" ref="B160:B162" si="4">ROW(B160) - ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>158</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>661</v>
-      </c>
-      <c r="D160" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>650</v>
+        <v>657</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>646</v>
       </c>
       <c r="F160" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G160" s="10" t="s">
-        <v>671</v>
+        <v>644</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>672</v>
       </c>
       <c r="H160" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="I160" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="J160" s="9">
-        <v>1</v>
-      </c>
-      <c r="K160" s="24" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="161" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+      <c r="I160" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="J160" s="7">
+        <v>4</v>
+      </c>
+      <c r="K160" s="20" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B161" s="11">
         <f t="shared" si="4"/>
         <v>159</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D161" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="J161" s="7"/>
+      <c r="K161" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="E161" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="I161" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J161" s="7">
-        <v>4</v>
-      </c>
-      <c r="K161" s="25" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="162" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B162" s="11">
-        <f t="shared" si="4"/>
+        <f>ROW(B162) - ROW($B$2)</f>
         <v>160</v>
       </c>
       <c r="C162" s="13" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>677</v>
+        <v>649</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F162" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J162" s="7"/>
-      <c r="K162" s="23" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="163" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="J162" s="7">
+        <v>1</v>
+      </c>
+      <c r="K162" s="18" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B163" s="11">
         <f>ROW(B163) - ROW($B$2)</f>
         <v>161</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>666</v>
+        <v>646</v>
       </c>
       <c r="F163" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J163" s="7">
-        <v>1</v>
-      </c>
-      <c r="K163" s="23" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="164" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="11">
-        <f>ROW(B164) - ROW($B$2)</f>
-        <v>162</v>
-      </c>
-      <c r="C164" s="13" t="s">
-        <v>661</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="E164" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="F164" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="G164" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="H164" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="I164" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="J164" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="K164" s="23" t="s">
-        <v>680</v>
+        <v>646</v>
+      </c>
+      <c r="J163" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="K163" s="18" t="s">
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -7895,8 +7830,8 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K160" r:id="rId1"/>
-    <hyperlink ref="K161" r:id="rId2"/>
+    <hyperlink ref="K159" r:id="rId1"/>
+    <hyperlink ref="K160" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
+++ b/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="681">
   <si>
     <t>#</t>
   </si>
@@ -300,6 +300,9 @@
     <t>J2</t>
   </si>
   <si>
+    <t>J3</t>
+  </si>
+  <si>
     <t>J4</t>
   </si>
   <si>
@@ -747,6 +750,9 @@
     <t>1x3P 18A -40℃~+105℃ 250V Orange 12~30 Direct Insert 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw Terminal Blocks ROHS</t>
   </si>
   <si>
+    <t>CABLE ADAPTER 6 POS</t>
+  </si>
+  <si>
     <t>Gold 250V 3A Straight Square Pins 2.5mm 3P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x3P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
@@ -1407,6 +1413,9 @@
     <t>BLM18PG221SN1D</t>
   </si>
   <si>
+    <t>TC2030-IDC</t>
+  </si>
+  <si>
     <t>X6511WV-03H-C60D30</t>
   </si>
   <si>
@@ -1678,6 +1687,9 @@
   </si>
   <si>
     <t>DORABO</t>
+  </si>
+  <si>
+    <t>Tag-Connect</t>
   </si>
   <si>
     <t>XKB</t>
@@ -2056,7 +2068,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2119,6 +2131,13 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2254,9 +2273,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2305,17 +2324,29 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2605,7 +2636,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2631,9 +2662,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2647,25 +2678,25 @@
         <v>36</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2681,19 +2712,19 @@
         <v>37</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="J3" s="7">
         <v>1</v>
@@ -2713,19 +2744,19 @@
         <v>38</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -2745,19 +2776,19 @@
         <v>39</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -2777,19 +2808,19 @@
         <v>40</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J6" s="9">
         <v>9</v>
@@ -2809,19 +2840,19 @@
         <v>41</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J7" s="7">
         <v>4</v>
@@ -2831,7 +2862,7 @@
     <row r="8" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
-        <f t="shared" ref="B8:B71" si="1">ROW(B8) - ROW($B$2)</f>
+        <f t="shared" ref="B8:B72" si="1">ROW(B8) - ROW($B$2)</f>
         <v>6</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -2841,19 +2872,19 @@
         <v>42</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="J8" s="9">
         <v>13</v>
@@ -2873,19 +2904,19 @@
         <v>43</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
@@ -2905,19 +2936,19 @@
         <v>44</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="J10" s="9">
         <v>4</v>
@@ -2937,19 +2968,19 @@
         <v>45</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="J11" s="7">
         <v>3</v>
@@ -2969,19 +3000,19 @@
         <v>46</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -3001,19 +3032,19 @@
         <v>47</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -3033,19 +3064,19 @@
         <v>48</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="J14" s="9">
         <v>5</v>
@@ -3062,22 +3093,22 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="J15" s="7">
         <v>62</v>
@@ -3094,22 +3125,22 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J16" s="9">
         <v>4</v>
@@ -3129,19 +3160,19 @@
         <v>49</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="J17" s="7">
         <v>6</v>
@@ -3161,19 +3192,19 @@
         <v>50</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -3193,19 +3224,19 @@
         <v>51</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="J19" s="7">
         <v>2</v>
@@ -3222,22 +3253,22 @@
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -3257,19 +3288,19 @@
         <v>52</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -3289,19 +3320,19 @@
         <v>53</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="J22" s="9">
         <v>8</v>
@@ -3321,19 +3352,19 @@
         <v>54</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -3353,19 +3384,19 @@
         <v>55</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="J24" s="7">
         <v>2</v>
@@ -3385,19 +3416,19 @@
         <v>56</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="J25" s="9">
         <v>1</v>
@@ -3417,19 +3448,19 @@
         <v>57</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="J26" s="7">
         <v>1</v>
@@ -3449,19 +3480,19 @@
         <v>58</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="J27" s="9">
         <v>1</v>
@@ -3481,19 +3512,19 @@
         <v>59</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="J28" s="7">
         <v>1</v>
@@ -3513,19 +3544,19 @@
         <v>60</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="J29" s="9">
         <v>1</v>
@@ -3545,19 +3576,19 @@
         <v>61</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="J30" s="7">
         <v>1</v>
@@ -3577,19 +3608,19 @@
         <v>62</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="J31" s="9">
         <v>6</v>
@@ -3609,19 +3640,19 @@
         <v>63</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="J32" s="7">
         <v>1</v>
@@ -3641,19 +3672,19 @@
         <v>64</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="J33" s="9">
         <v>3</v>
@@ -3673,19 +3704,19 @@
         <v>65</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="J34" s="7">
         <v>2</v>
@@ -3705,19 +3736,19 @@
         <v>66</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J35" s="9">
         <v>2</v>
@@ -3737,19 +3768,19 @@
         <v>67</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J36" s="7">
         <v>1</v>
@@ -3769,19 +3800,19 @@
         <v>68</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J37" s="9">
         <v>1</v>
@@ -3801,19 +3832,19 @@
         <v>69</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J38" s="7">
         <v>1</v>
@@ -3833,19 +3864,19 @@
         <v>70</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J39" s="9">
         <v>1</v>
@@ -3865,19 +3896,19 @@
         <v>71</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J40" s="7">
         <v>1</v>
@@ -3897,19 +3928,19 @@
         <v>72</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J41" s="9">
         <v>5</v>
@@ -3929,19 +3960,19 @@
         <v>73</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J42" s="7">
         <v>5</v>
@@ -3961,19 +3992,19 @@
         <v>74</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J43" s="9">
         <v>1</v>
@@ -3993,19 +4024,19 @@
         <v>75</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J44" s="7">
         <v>1</v>
@@ -4025,19 +4056,19 @@
         <v>76</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J45" s="9">
         <v>1</v>
@@ -4057,19 +4088,19 @@
         <v>77</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J46" s="7">
         <v>1</v>
@@ -4089,19 +4120,19 @@
         <v>78</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J47" s="9">
         <v>8</v>
@@ -4121,19 +4152,19 @@
         <v>79</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J48" s="7">
         <v>6</v>
@@ -4153,19 +4184,19 @@
         <v>80</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J49" s="9">
         <v>4</v>
@@ -4185,19 +4216,19 @@
         <v>81</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J50" s="7">
         <v>4</v>
@@ -4217,19 +4248,19 @@
         <v>82</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J51" s="9">
         <v>8</v>
@@ -4249,19 +4280,19 @@
         <v>83</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J52" s="7">
         <v>8</v>
@@ -4281,19 +4312,19 @@
         <v>84</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J53" s="9">
         <v>1</v>
@@ -4313,19 +4344,19 @@
         <v>85</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J54" s="7">
         <v>1</v>
@@ -4345,19 +4376,19 @@
         <v>86</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H55" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J55" s="9">
         <v>2</v>
@@ -4377,19 +4408,19 @@
         <v>87</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J56" s="7">
         <v>1</v>
@@ -4409,19 +4440,19 @@
         <v>88</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J57" s="9">
         <v>6</v>
@@ -4441,19 +4472,19 @@
         <v>89</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J58" s="7">
         <v>1</v>
@@ -4473,19 +4504,19 @@
         <v>90</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J59" s="9">
         <v>4</v>
@@ -4505,19 +4536,19 @@
         <v>91</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J60" s="7">
         <v>1</v>
@@ -4537,115 +4568,117 @@
         <v>92</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J61" s="9">
         <v>1</v>
       </c>
       <c r="K61" s="9"/>
     </row>
-    <row r="62" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="11">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="C62" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="D62" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="I62" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J62" s="9">
-        <v>1</v>
-      </c>
-      <c r="K62" s="9"/>
-    </row>
-    <row r="63" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E62" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="J62" s="19">
+        <v>1</v>
+      </c>
+      <c r="K62" s="23" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="7" t="s">
+      <c r="C63" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E63" s="8" t="s">
-        <v>243</v>
+      <c r="E63" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>554</v>
+        <v>360</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>557</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J63" s="7">
-        <v>1</v>
-      </c>
-      <c r="K63" s="7"/>
-    </row>
-    <row r="64" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J63" s="9">
+        <v>1</v>
+      </c>
+      <c r="K63" s="9"/>
+    </row>
+    <row r="64" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="11">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D64" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>644</v>
-      </c>
       <c r="G64" s="8" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J64" s="7">
         <v>1</v>
@@ -4658,95 +4691,95 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>258</v>
+      <c r="D65" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>555</v>
+        <v>648</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>559</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J65" s="9">
-        <v>1</v>
-      </c>
-      <c r="K65" s="9"/>
-    </row>
-    <row r="66" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J65" s="7">
+        <v>1</v>
+      </c>
+      <c r="K65" s="7"/>
+    </row>
+    <row r="66" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>95</v>
+        <v>651</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="J66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="11">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="7" t="s">
+      <c r="C67" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E67" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>553</v>
+      <c r="E67" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>559</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J67" s="7">
-        <v>6</v>
-      </c>
-      <c r="K67" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J67" s="9">
+        <v>2</v>
+      </c>
+      <c r="K67" s="9"/>
     </row>
     <row r="68" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -4754,95 +4787,95 @@
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="9" t="s">
+      <c r="C68" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>556</v>
+      <c r="E68" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>557</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J68" s="9">
-        <v>2</v>
-      </c>
-      <c r="K68" s="9"/>
-    </row>
-    <row r="69" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J68" s="7">
+        <v>6</v>
+      </c>
+      <c r="K68" s="7"/>
+    </row>
+    <row r="69" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D69" s="7" t="s">
+      <c r="C69" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>247</v>
+      <c r="E69" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>555</v>
+        <v>648</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>560</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J69" s="7">
-        <v>1</v>
-      </c>
-      <c r="K69" s="7"/>
-    </row>
-    <row r="70" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J69" s="9">
+        <v>2</v>
+      </c>
+      <c r="K69" s="9"/>
+    </row>
+    <row r="70" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="C70" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" s="9" t="s">
+      <c r="C70" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>248</v>
+      <c r="E70" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>552</v>
+        <v>648</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>559</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J70" s="9">
-        <v>2</v>
-      </c>
-      <c r="K70" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J70" s="7">
+        <v>1</v>
+      </c>
+      <c r="K70" s="7"/>
     </row>
     <row r="71" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
@@ -4850,95 +4883,95 @@
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E71" s="8" t="s">
-        <v>249</v>
+      <c r="E71" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>552</v>
+        <v>648</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>555</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J71" s="7">
+        <v>650</v>
+      </c>
+      <c r="J71" s="9">
         <v>2</v>
       </c>
-      <c r="K71" s="7"/>
-    </row>
-    <row r="72" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K71" s="9"/>
+    </row>
+    <row r="72" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
-        <f t="shared" ref="B72:B135" si="2">ROW(B72) - ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" s="9" t="s">
+      <c r="C72" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>250</v>
+      <c r="E72" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>557</v>
+        <v>648</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J72" s="9">
+        <v>650</v>
+      </c>
+      <c r="J72" s="7">
         <v>2</v>
       </c>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="73" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K72" s="7"/>
+    </row>
+    <row r="73" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="B73:B136" si="2">ROW(B73) - ROW($B$2)</f>
         <v>71</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="7" t="s">
+      <c r="C73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E73" s="8" t="s">
-        <v>251</v>
+      <c r="E73" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>552</v>
+        <v>648</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J73" s="7">
+        <v>650</v>
+      </c>
+      <c r="J73" s="9">
         <v>2</v>
       </c>
-      <c r="K73" s="7"/>
+      <c r="K73" s="9"/>
     </row>
     <row r="74" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -4946,31 +4979,31 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D74" s="9" t="s">
+      <c r="D74" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>252</v>
+      <c r="E74" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>552</v>
+        <v>648</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J74" s="9">
+        <v>650</v>
+      </c>
+      <c r="J74" s="7">
         <v>2</v>
       </c>
-      <c r="K74" s="9"/>
+      <c r="K74" s="7"/>
     </row>
     <row r="75" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
@@ -4978,31 +5011,31 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E75" s="8" t="s">
-        <v>253</v>
+      <c r="E75" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>552</v>
+        <v>648</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>555</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J75" s="7">
+        <v>650</v>
+      </c>
+      <c r="J75" s="9">
         <v>2</v>
       </c>
-      <c r="K75" s="7"/>
+      <c r="K75" s="9"/>
     </row>
     <row r="76" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -5010,31 +5043,31 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="D76" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>254</v>
+      <c r="E76" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="H76" s="9" t="s">
-        <v>552</v>
+        <v>648</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J76" s="9">
+        <v>650</v>
+      </c>
+      <c r="J76" s="7">
         <v>2</v>
       </c>
-      <c r="K76" s="9"/>
+      <c r="K76" s="7"/>
     </row>
     <row r="77" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
@@ -5042,31 +5075,31 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E77" s="8" t="s">
-        <v>255</v>
+      <c r="E77" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>556</v>
+        <v>648</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>555</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J77" s="7">
+        <v>650</v>
+      </c>
+      <c r="J77" s="9">
         <v>2</v>
       </c>
-      <c r="K77" s="7"/>
+      <c r="K77" s="9"/>
     </row>
     <row r="78" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -5074,31 +5107,31 @@
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="9" t="s">
+      <c r="C78" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E78" s="10" t="s">
-        <v>256</v>
+      <c r="E78" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>558</v>
+        <v>648</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J78" s="9">
-        <v>1</v>
-      </c>
-      <c r="K78" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J78" s="7">
+        <v>2</v>
+      </c>
+      <c r="K78" s="7"/>
     </row>
     <row r="79" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -5106,95 +5139,95 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C79" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="7" t="s">
+      <c r="C79" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E79" s="8" t="s">
-        <v>257</v>
+      <c r="E79" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>556</v>
+        <v>648</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>562</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J79" s="7">
-        <v>1</v>
-      </c>
-      <c r="K79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J79" s="9">
+        <v>1</v>
+      </c>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="11">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" s="9" t="s">
+      <c r="C80" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E80" s="10" t="s">
-        <v>260</v>
+      <c r="E80" s="8" t="s">
+        <v>259</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>544</v>
+        <v>648</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>560</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="J80" s="9">
-        <v>1</v>
-      </c>
-      <c r="K80" s="9"/>
-    </row>
-    <row r="81" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J80" s="7">
+        <v>1</v>
+      </c>
+      <c r="K80" s="7"/>
+    </row>
+    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="11">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E81" s="8" t="s">
-        <v>261</v>
+      <c r="E81" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="J81" s="7">
-        <v>1</v>
-      </c>
-      <c r="K81" s="7"/>
+        <v>648</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="J81" s="9">
+        <v>1</v>
+      </c>
+      <c r="K81" s="9"/>
     </row>
     <row r="82" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
@@ -5202,31 +5235,31 @@
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D82" s="9" t="s">
+      <c r="C82" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E82" s="10" t="s">
-        <v>262</v>
+      <c r="E82" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J82" s="9">
-        <v>5</v>
-      </c>
-      <c r="K82" s="9"/>
+        <v>648</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="J82" s="7">
+        <v>1</v>
+      </c>
+      <c r="K82" s="7"/>
     </row>
     <row r="83" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
@@ -5234,31 +5267,31 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E83" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>560</v>
+      <c r="E83" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>564</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J83" s="7">
-        <v>1</v>
-      </c>
-      <c r="K83" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J83" s="9">
+        <v>5</v>
+      </c>
+      <c r="K83" s="9"/>
     </row>
     <row r="84" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -5266,31 +5299,31 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E84" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>560</v>
+      <c r="E84" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>564</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J84" s="9">
-        <v>2</v>
-      </c>
-      <c r="K84" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J84" s="7">
+        <v>1</v>
+      </c>
+      <c r="K84" s="7"/>
     </row>
     <row r="85" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -5298,63 +5331,63 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C85" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" s="7" t="s">
+      <c r="C85" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E85" s="8" t="s">
-        <v>265</v>
+      <c r="E85" s="10" t="s">
+        <v>266</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>561</v>
+        <v>380</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>564</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J85" s="7">
-        <v>9</v>
-      </c>
-      <c r="K85" s="7"/>
-    </row>
-    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J85" s="9">
+        <v>2</v>
+      </c>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="86" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="11">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C86" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" s="9" t="s">
+      <c r="C86" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E86" s="10" t="s">
-        <v>266</v>
+      <c r="E86" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>10</v>
+        <v>648</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J86" s="9">
-        <v>1</v>
-      </c>
-      <c r="K86" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J86" s="7">
+        <v>9</v>
+      </c>
+      <c r="K86" s="7"/>
     </row>
     <row r="87" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
@@ -5362,63 +5395,63 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D87" s="7" t="s">
+      <c r="C87" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E87" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>545</v>
+      <c r="E87" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J87" s="7">
-        <v>1</v>
-      </c>
-      <c r="K87" s="7"/>
-    </row>
-    <row r="88" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J87" s="9">
+        <v>1</v>
+      </c>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="11">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C88" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D88" s="9" t="s">
+      <c r="C88" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E88" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>562</v>
+      <c r="E88" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>548</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J88" s="9">
-        <v>5</v>
-      </c>
-      <c r="K88" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J88" s="7">
+        <v>1</v>
+      </c>
+      <c r="K88" s="7"/>
     </row>
     <row r="89" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
@@ -5426,127 +5459,127 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" s="7" t="s">
+      <c r="C89" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E89" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>563</v>
+      <c r="E89" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>566</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J89" s="7">
-        <v>4</v>
-      </c>
-      <c r="K89" s="7"/>
-    </row>
-    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J89" s="9">
+        <v>5</v>
+      </c>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="11">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="9" t="s">
+      <c r="C90" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E90" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>542</v>
+      <c r="E90" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J90" s="9">
-        <v>1</v>
-      </c>
-      <c r="K90" s="9"/>
-    </row>
-    <row r="91" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J90" s="7">
+        <v>4</v>
+      </c>
+      <c r="K90" s="7"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="11">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C91" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D91" s="7" t="s">
+      <c r="C91" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E91" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>564</v>
+      <c r="E91" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J91" s="7">
-        <v>6</v>
-      </c>
-      <c r="K91" s="7"/>
-    </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J91" s="9">
+        <v>1</v>
+      </c>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="11">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>29</v>
+      <c r="C92" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>651</v>
+        <v>121</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>474</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I92" s="8" t="s">
-        <v>603</v>
+        <v>568</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="J92" s="7">
-        <v>3</v>
-      </c>
-      <c r="K92" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="K92" s="7"/>
     </row>
     <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -5554,31 +5587,31 @@
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>121</v>
+        <v>655</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J93" s="7">
-        <v>1</v>
-      </c>
-      <c r="K93" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="K93" s="9"/>
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -5586,31 +5619,31 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D94" s="9" t="s">
+      <c r="D94" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E94" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I94" s="10" t="s">
-        <v>605</v>
-      </c>
-      <c r="J94" s="9">
-        <v>1</v>
-      </c>
-      <c r="K94" s="9"/>
+      <c r="E94" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1</v>
+      </c>
+      <c r="K94" s="7"/>
     </row>
     <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
@@ -5619,7 +5652,7 @@
         <v>93</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>123</v>
@@ -5628,16 +5661,16 @@
         <v>275</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="J95" s="9">
         <v>1</v>
@@ -5650,31 +5683,31 @@
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E96" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I96" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="J96" s="7">
-        <v>1</v>
-      </c>
-      <c r="K96" s="7"/>
+      <c r="E96" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I96" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="J96" s="9">
+        <v>1</v>
+      </c>
+      <c r="K96" s="9"/>
     </row>
     <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
@@ -5685,28 +5718,28 @@
       <c r="C97" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D97" s="9" t="s">
+      <c r="D97" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E97" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I97" s="10" t="s">
-        <v>608</v>
-      </c>
-      <c r="J97" s="9">
-        <v>1</v>
-      </c>
-      <c r="K97" s="9"/>
+      <c r="E97" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="J97" s="7">
+        <v>1</v>
+      </c>
+      <c r="K97" s="7"/>
     </row>
     <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
@@ -5717,126 +5750,126 @@
       <c r="C98" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E98" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="J98" s="7">
-        <v>6</v>
-      </c>
-      <c r="K98" s="7"/>
-    </row>
-    <row r="99" spans="1:11" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E98" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I98" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="J98" s="9">
+        <v>1</v>
+      </c>
+      <c r="K98" s="9"/>
+    </row>
+    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="11">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D99" s="9" t="s">
+      <c r="D99" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E99" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I99" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="J99" s="9">
-        <v>172</v>
-      </c>
-      <c r="K99" s="9"/>
-    </row>
-    <row r="100" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="J99" s="7">
+        <v>6</v>
+      </c>
+      <c r="K99" s="7"/>
+    </row>
+    <row r="100" spans="1:11" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="11">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="C100" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="J100" s="7">
-        <v>42</v>
-      </c>
-      <c r="K100" s="7"/>
-    </row>
-    <row r="101" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C100" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="J100" s="9">
+        <v>172</v>
+      </c>
+      <c r="K100" s="9"/>
+    </row>
+    <row r="101" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="11">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I101" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="J101" s="9">
-        <v>12</v>
-      </c>
-      <c r="K101" s="9"/>
-    </row>
-    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D101" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="J101" s="7">
+        <v>42</v>
+      </c>
+      <c r="K101" s="7"/>
+    </row>
+    <row r="102" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="11">
         <f t="shared" si="2"/>
@@ -5845,28 +5878,28 @@
       <c r="C102" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E102" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="G102" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I102" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="J102" s="7">
-        <v>4</v>
-      </c>
-      <c r="K102" s="7"/>
+      <c r="E102" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="J102" s="9">
+        <v>12</v>
+      </c>
+      <c r="K102" s="9"/>
     </row>
     <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -5877,30 +5910,28 @@
       <c r="C103" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D103" s="14" t="s">
+      <c r="D103" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E103" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="H103" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="I103" s="15" t="s">
-        <v>614</v>
-      </c>
-      <c r="J103" s="14">
-        <v>3</v>
-      </c>
-      <c r="K103" s="16" t="s">
-        <v>641</v>
-      </c>
+      <c r="E103" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="J103" s="7">
+        <v>4</v>
+      </c>
+      <c r="K103" s="7"/>
     </row>
     <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
@@ -5911,28 +5942,30 @@
       <c r="C104" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E104" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="J104" s="7">
-        <v>4</v>
-      </c>
-      <c r="K104" s="7"/>
+      <c r="E104" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="J104" s="14">
+        <v>3</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
@@ -5943,28 +5976,28 @@
       <c r="C105" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D105" s="9" t="s">
+      <c r="D105" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E105" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F105" s="9" t="s">
+      <c r="E105" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F105" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G105" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I105" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="J105" s="9">
-        <v>1</v>
-      </c>
-      <c r="K105" s="9"/>
+      <c r="G105" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="J105" s="7">
+        <v>4</v>
+      </c>
+      <c r="K105" s="7"/>
     </row>
     <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
@@ -5975,30 +6008,30 @@
       <c r="C106" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E106" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="J106" s="7">
-        <v>3</v>
-      </c>
-      <c r="K106" s="7"/>
-    </row>
-    <row r="107" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E106" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="J106" s="9">
+        <v>1</v>
+      </c>
+      <c r="K106" s="9"/>
+    </row>
+    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="11">
         <f t="shared" si="2"/>
@@ -6007,60 +6040,60 @@
       <c r="C107" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D107" s="9" t="s">
+      <c r="D107" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E107" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I107" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="J107" s="9">
-        <v>16</v>
-      </c>
-      <c r="K107" s="9"/>
-    </row>
-    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="J107" s="7">
+        <v>3</v>
+      </c>
+      <c r="K107" s="7"/>
+    </row>
+    <row r="108" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="11">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E108" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I108" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="J108" s="7">
-        <v>1</v>
-      </c>
-      <c r="K108" s="7"/>
+      <c r="E108" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I108" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J108" s="9">
+        <v>16</v>
+      </c>
+      <c r="K108" s="9"/>
     </row>
     <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
@@ -6068,31 +6101,31 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D109" s="9" t="s">
+      <c r="D109" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="F109" s="9" t="s">
+      <c r="E109" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F109" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G109" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I109" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="J109" s="9">
-        <v>1</v>
-      </c>
-      <c r="K109" s="9"/>
+      <c r="G109" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="J109" s="7">
+        <v>1</v>
+      </c>
+      <c r="K109" s="7"/>
     </row>
     <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
@@ -6100,31 +6133,31 @@
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E110" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I110" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="J110" s="7">
-        <v>1</v>
-      </c>
-      <c r="K110" s="7"/>
+      <c r="E110" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J110" s="9">
+        <v>1</v>
+      </c>
+      <c r="K110" s="9"/>
     </row>
     <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
@@ -6132,31 +6165,31 @@
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D111" s="9" t="s">
+      <c r="D111" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E111" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G111" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I111" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="J111" s="9">
-        <v>2</v>
-      </c>
-      <c r="K111" s="9"/>
+      <c r="E111" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="J111" s="7">
+        <v>1</v>
+      </c>
+      <c r="K111" s="7"/>
     </row>
     <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
@@ -6164,95 +6197,95 @@
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E112" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F112" s="7" t="s">
+      <c r="E112" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F112" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="G112" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="J112" s="7">
-        <v>6</v>
-      </c>
-      <c r="K112" s="7"/>
-    </row>
-    <row r="113" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G112" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="J112" s="9">
+        <v>2</v>
+      </c>
+      <c r="K112" s="9"/>
+    </row>
+    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="11">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D113" s="9" t="s">
+      <c r="D113" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E113" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G113" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I113" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="J113" s="9">
-        <v>9</v>
-      </c>
-      <c r="K113" s="9"/>
-    </row>
-    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E113" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="J113" s="7">
+        <v>6</v>
+      </c>
+      <c r="K113" s="7"/>
+    </row>
+    <row r="114" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="11">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E114" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G114" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="J114" s="7">
-        <v>2</v>
-      </c>
-      <c r="K114" s="7"/>
+      <c r="E114" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="J114" s="9">
+        <v>9</v>
+      </c>
+      <c r="K114" s="9"/>
     </row>
     <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
@@ -6260,31 +6293,31 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D115" s="9" t="s">
+      <c r="D115" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E115" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="F115" s="9" t="s">
+      <c r="E115" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G115" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I115" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="J115" s="9">
-        <v>4</v>
-      </c>
-      <c r="K115" s="9"/>
+      <c r="G115" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="J115" s="7">
+        <v>2</v>
+      </c>
+      <c r="K115" s="7"/>
     </row>
     <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
@@ -6292,31 +6325,31 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E116" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I116" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="J116" s="7">
-        <v>1</v>
-      </c>
-      <c r="K116" s="7"/>
+      <c r="E116" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="J116" s="9">
+        <v>4</v>
+      </c>
+      <c r="K116" s="9"/>
     </row>
     <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
@@ -6324,33 +6357,31 @@
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D117" s="14" t="s">
+      <c r="D117" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E117" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="F117" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="G117" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="H117" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="I117" s="15" t="s">
-        <v>614</v>
-      </c>
-      <c r="J117" s="14">
-        <v>1</v>
-      </c>
-      <c r="K117" s="16" t="s">
-        <v>641</v>
-      </c>
+      <c r="E117" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="J117" s="7">
+        <v>1</v>
+      </c>
+      <c r="K117" s="7"/>
     </row>
     <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
@@ -6361,92 +6392,94 @@
       <c r="C118" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D118" s="9" t="s">
+      <c r="D118" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="E118" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="H118" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I118" s="10" t="s">
-        <v>626</v>
-      </c>
-      <c r="J118" s="9">
-        <v>4</v>
-      </c>
-      <c r="K118" s="9"/>
-    </row>
-    <row r="119" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E118" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="G118" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="H118" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="I118" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="J118" s="14">
+        <v>1</v>
+      </c>
+      <c r="K118" s="16" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="11">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="D119" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E119" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="I119" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="J119" s="7">
-        <v>8</v>
-      </c>
-      <c r="K119" s="7"/>
-    </row>
-    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E119" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="J119" s="9">
+        <v>4</v>
+      </c>
+      <c r="K119" s="9"/>
+    </row>
+    <row r="120" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="11">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="C120" s="13" t="s">
+      <c r="C120" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D120" s="9" t="s">
+      <c r="D120" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E120" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="F120" s="9" t="s">
+      <c r="E120" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="F120" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G120" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I120" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="J120" s="9">
-        <v>4</v>
-      </c>
-      <c r="K120" s="9"/>
+      <c r="G120" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="J120" s="7">
+        <v>8</v>
+      </c>
+      <c r="K120" s="7"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
@@ -6454,31 +6487,31 @@
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D121" s="7" t="s">
+      <c r="D121" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E121" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I121" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="J121" s="7">
-        <v>6</v>
-      </c>
-      <c r="K121" s="7"/>
+      <c r="E121" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I121" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="J121" s="9">
+        <v>4</v>
+      </c>
+      <c r="K121" s="9"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
@@ -6486,33 +6519,31 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D122" s="14" t="s">
+      <c r="D122" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E122" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="F122" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="G122" s="15" t="s">
-        <v>499</v>
-      </c>
-      <c r="H122" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="I122" s="15" t="s">
+      <c r="E122" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I122" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="J122" s="14">
-        <v>2</v>
-      </c>
-      <c r="K122" s="16" t="s">
-        <v>641</v>
-      </c>
+      <c r="J122" s="7">
+        <v>6</v>
+      </c>
+      <c r="K122" s="7"/>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
@@ -6520,31 +6551,33 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="D123" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E123" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G123" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I123" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="J123" s="7">
-        <v>1</v>
-      </c>
-      <c r="K123" s="7"/>
+      <c r="E123" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="G123" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="H123" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="I123" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="J123" s="14">
+        <v>2</v>
+      </c>
+      <c r="K123" s="16" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
@@ -6552,31 +6585,31 @@
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="C124" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D124" s="9" t="s">
+      <c r="C124" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D124" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G124" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I124" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="J124" s="9">
-        <v>1</v>
-      </c>
-      <c r="K124" s="9"/>
+      <c r="E124" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="J124" s="7">
+        <v>1</v>
+      </c>
+      <c r="K124" s="7"/>
     </row>
     <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
@@ -6584,31 +6617,31 @@
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G125" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="J125" s="7">
-        <v>6</v>
-      </c>
-      <c r="K125" s="7"/>
+      <c r="C125" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I125" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="J125" s="9">
+        <v>1</v>
+      </c>
+      <c r="K125" s="9"/>
     </row>
     <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
@@ -6616,31 +6649,31 @@
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="H126" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I126" s="10" t="s">
-        <v>631</v>
-      </c>
-      <c r="J126" s="9">
-        <v>1</v>
-      </c>
-      <c r="K126" s="9"/>
+      <c r="D126" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="J126" s="7">
+        <v>6</v>
+      </c>
+      <c r="K126" s="7"/>
     </row>
     <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
@@ -6648,31 +6681,31 @@
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="D127" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E127" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I127" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="J127" s="7">
-        <v>1</v>
-      </c>
-      <c r="K127" s="7"/>
+      <c r="E127" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I127" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="J127" s="9">
+        <v>1</v>
+      </c>
+      <c r="K127" s="9"/>
     </row>
     <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
@@ -6680,31 +6713,31 @@
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="C128" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D128" s="9" t="s">
+      <c r="C128" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D128" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E128" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="G128" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I128" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="J128" s="9">
-        <v>1</v>
-      </c>
-      <c r="K128" s="9"/>
+      <c r="E128" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="J128" s="7">
+        <v>1</v>
+      </c>
+      <c r="K128" s="7"/>
     </row>
     <row r="129" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
@@ -6712,31 +6745,31 @@
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D129" s="7" t="s">
+      <c r="C129" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E129" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="G129" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="I129" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="J129" s="7">
-        <v>1</v>
-      </c>
-      <c r="K129" s="7"/>
+      <c r="E129" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I129" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="J129" s="9">
+        <v>1</v>
+      </c>
+      <c r="K129" s="9"/>
     </row>
     <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
@@ -6744,31 +6777,31 @@
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
-      <c r="C130" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D130" s="9" t="s">
+      <c r="C130" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E130" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="G130" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="H130" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I130" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="J130" s="9">
-        <v>1</v>
-      </c>
-      <c r="K130" s="9"/>
+      <c r="E130" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="J130" s="7">
+        <v>1</v>
+      </c>
+      <c r="K130" s="7"/>
     </row>
     <row r="131" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
@@ -6777,7 +6810,7 @@
         <v>129</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>157</v>
@@ -6786,19 +6819,19 @@
         <v>308</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="J131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" s="9"/>
     </row>
@@ -6808,191 +6841,191 @@
         <f t="shared" si="2"/>
         <v>130</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D132" s="7" t="s">
+      <c r="C132" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D132" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E132" s="8" t="s">
-        <v>309</v>
+      <c r="E132" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J132" s="7">
-        <v>7</v>
-      </c>
-      <c r="K132" s="7"/>
-    </row>
-    <row r="133" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="J132" s="9">
+        <v>2</v>
+      </c>
+      <c r="K132" s="9"/>
+    </row>
+    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="11">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
-      <c r="C133" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D133" s="9" t="s">
+      <c r="C133" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E133" s="10" t="s">
-        <v>310</v>
+      <c r="E133" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G133" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>567</v>
+        <v>648</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>570</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J133" s="9">
-        <v>1</v>
-      </c>
-      <c r="K133" s="9"/>
-    </row>
-    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J133" s="7">
+        <v>7</v>
+      </c>
+      <c r="K133" s="7"/>
+    </row>
+    <row r="134" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="11">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="C134" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D134" s="7" t="s">
+      <c r="C134" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E134" s="8" t="s">
-        <v>311</v>
+      <c r="E134" s="10" t="s">
+        <v>312</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G134" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>568</v>
+        <v>648</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>571</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J134" s="7">
-        <v>1</v>
-      </c>
-      <c r="K134" s="7"/>
-    </row>
-    <row r="135" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J134" s="9">
+        <v>1</v>
+      </c>
+      <c r="K134" s="9"/>
+    </row>
+    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="11">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="C135" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D135" s="9" t="s">
+      <c r="C135" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D135" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E135" s="10" t="s">
-        <v>312</v>
+      <c r="E135" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>569</v>
+        <v>648</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>572</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J135" s="9">
-        <v>1</v>
-      </c>
-      <c r="K135" s="9"/>
-    </row>
-    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J135" s="7">
+        <v>1</v>
+      </c>
+      <c r="K135" s="7"/>
+    </row>
+    <row r="136" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="11">
-        <f t="shared" ref="B136:B157" si="3">ROW(B136) - ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="D136" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E136" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="H136" s="7" t="s">
-        <v>569</v>
+      <c r="E136" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J136" s="7">
-        <v>1</v>
-      </c>
-      <c r="K136" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J136" s="9">
+        <v>1</v>
+      </c>
+      <c r="K136" s="9"/>
     </row>
     <row r="137" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="B137:B158" si="3">ROW(B137) - ROW($B$2)</f>
         <v>135</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D137" s="9" t="s">
+      <c r="D137" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E137" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>543</v>
+      <c r="E137" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>573</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J137" s="9">
-        <v>1</v>
-      </c>
-      <c r="K137" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J137" s="7">
+        <v>1</v>
+      </c>
+      <c r="K137" s="7"/>
     </row>
     <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
@@ -7000,31 +7033,31 @@
         <f t="shared" si="3"/>
         <v>136</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E138" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>543</v>
+      <c r="E138" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J138" s="7">
-        <v>1</v>
-      </c>
-      <c r="K138" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J138" s="9">
+        <v>1</v>
+      </c>
+      <c r="K138" s="9"/>
     </row>
     <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
@@ -7032,31 +7065,31 @@
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D139" s="9" t="s">
+      <c r="D139" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E139" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>570</v>
+      <c r="E139" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J139" s="9">
-        <v>1</v>
-      </c>
-      <c r="K139" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J139" s="7">
+        <v>1</v>
+      </c>
+      <c r="K139" s="7"/>
     </row>
     <row r="140" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
@@ -7064,63 +7097,63 @@
         <f t="shared" si="3"/>
         <v>138</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E140" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>543</v>
+      <c r="E140" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>574</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J140" s="7">
-        <v>1</v>
-      </c>
-      <c r="K140" s="7"/>
-    </row>
-    <row r="141" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J140" s="9">
+        <v>1</v>
+      </c>
+      <c r="K140" s="9"/>
+    </row>
+    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="11">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
-      <c r="C141" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="9" t="s">
+      <c r="C141" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E141" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="G141" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>545</v>
+      <c r="E141" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J141" s="9">
-        <v>2</v>
-      </c>
-      <c r="K141" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J141" s="7">
+        <v>1</v>
+      </c>
+      <c r="K141" s="7"/>
     </row>
     <row r="142" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
@@ -7128,63 +7161,63 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="C142" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D142" s="7" t="s">
+      <c r="C142" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E142" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>571</v>
+      <c r="E142" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J142" s="7">
-        <v>1</v>
-      </c>
-      <c r="K142" s="7"/>
-    </row>
-    <row r="143" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J142" s="9">
+        <v>2</v>
+      </c>
+      <c r="K142" s="9"/>
+    </row>
+    <row r="143" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="11">
         <f t="shared" si="3"/>
         <v>141</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D143" s="9" t="s">
+      <c r="D143" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="E143" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>569</v>
+      <c r="E143" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>575</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J143" s="9">
-        <v>3</v>
-      </c>
-      <c r="K143" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J143" s="7">
+        <v>1</v>
+      </c>
+      <c r="K143" s="7"/>
     </row>
     <row r="144" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
@@ -7192,31 +7225,31 @@
         <f t="shared" si="3"/>
         <v>142</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="D144" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E144" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>569</v>
+      <c r="E144" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J144" s="7">
-        <v>2</v>
-      </c>
-      <c r="K144" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J144" s="9">
+        <v>3</v>
+      </c>
+      <c r="K144" s="9"/>
     </row>
     <row r="145" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
@@ -7224,31 +7257,31 @@
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C145" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D145" s="9" t="s">
+      <c r="D145" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E145" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F145" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>569</v>
+      <c r="E145" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>573</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J145" s="9">
-        <v>3</v>
-      </c>
-      <c r="K145" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J145" s="7">
+        <v>2</v>
+      </c>
+      <c r="K145" s="7"/>
     </row>
     <row r="146" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
@@ -7256,31 +7289,31 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F146" s="7" t="s">
+      <c r="F146" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="G146" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>570</v>
+      <c r="G146" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J146" s="7">
-        <v>1</v>
-      </c>
-      <c r="K146" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J146" s="9">
+        <v>3</v>
+      </c>
+      <c r="K146" s="9"/>
     </row>
     <row r="147" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
@@ -7291,30 +7324,30 @@
       <c r="C147" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="9" t="s">
+      <c r="D147" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E147" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>542</v>
+      <c r="E147" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>574</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J147" s="9">
-        <v>1</v>
-      </c>
-      <c r="K147" s="9"/>
-    </row>
-    <row r="148" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J147" s="7">
+        <v>1</v>
+      </c>
+      <c r="K147" s="7"/>
+    </row>
+    <row r="148" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="11">
         <f t="shared" si="3"/>
@@ -7323,60 +7356,60 @@
       <c r="C148" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="D148" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E148" s="8" t="s">
-        <v>324</v>
+      <c r="E148" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>572</v>
+        <v>648</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="I148" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J148" s="7">
-        <v>8</v>
-      </c>
-      <c r="K148" s="7"/>
-    </row>
-    <row r="149" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J148" s="9">
+        <v>1</v>
+      </c>
+      <c r="K148" s="9"/>
+    </row>
+    <row r="149" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="11">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C149" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D149" s="9" t="s">
+      <c r="D149" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="E149" s="10" t="s">
-        <v>325</v>
+      <c r="E149" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>569</v>
+        <v>648</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>576</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J149" s="9">
-        <v>1</v>
-      </c>
-      <c r="K149" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J149" s="7">
+        <v>8</v>
+      </c>
+      <c r="K149" s="7"/>
     </row>
     <row r="150" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
@@ -7384,31 +7417,31 @@
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
-      <c r="C150" s="12" t="s">
+      <c r="C150" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="E150" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>569</v>
+      <c r="E150" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J150" s="7">
-        <v>1</v>
-      </c>
-      <c r="K150" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J150" s="9">
+        <v>1</v>
+      </c>
+      <c r="K150" s="9"/>
     </row>
     <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
@@ -7416,31 +7449,31 @@
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
-      <c r="C151" s="13" t="s">
+      <c r="C151" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D151" s="9" t="s">
+      <c r="D151" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E151" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>569</v>
+      <c r="E151" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>573</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J151" s="9">
-        <v>1</v>
-      </c>
-      <c r="K151" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J151" s="7">
+        <v>1</v>
+      </c>
+      <c r="K151" s="7"/>
     </row>
     <row r="152" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
@@ -7448,31 +7481,31 @@
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="C152" s="12" t="s">
+      <c r="C152" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="D152" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E152" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>569</v>
+      <c r="E152" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>573</v>
       </c>
       <c r="I152" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J152" s="7">
-        <v>1</v>
-      </c>
-      <c r="K152" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J152" s="9">
+        <v>1</v>
+      </c>
+      <c r="K152" s="9"/>
     </row>
     <row r="153" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
@@ -7480,31 +7513,31 @@
         <f t="shared" si="3"/>
         <v>151</v>
       </c>
-      <c r="C153" s="13" t="s">
+      <c r="C153" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="9" t="s">
+      <c r="D153" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E153" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F153" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="G153" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>569</v>
+      <c r="E153" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>573</v>
       </c>
       <c r="I153" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J153" s="9">
-        <v>1</v>
-      </c>
-      <c r="K153" s="9"/>
+        <v>650</v>
+      </c>
+      <c r="J153" s="7">
+        <v>1</v>
+      </c>
+      <c r="K153" s="7"/>
     </row>
     <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
@@ -7512,33 +7545,34 @@
         <f t="shared" si="3"/>
         <v>152</v>
       </c>
-      <c r="C154" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D154" s="7" t="s">
+      <c r="C154" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="E154" s="8" t="s">
-        <v>330</v>
+      <c r="E154" s="10" t="s">
+        <v>331</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H154" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="H154" s="9" t="s">
         <v>573</v>
       </c>
       <c r="I154" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="J154" s="7">
-        <v>2</v>
-      </c>
-      <c r="K154" s="7"/>
+        <v>650</v>
+      </c>
+      <c r="J154" s="9">
+        <v>1</v>
+      </c>
+      <c r="K154" s="9"/>
     </row>
     <row r="155" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="1"/>
       <c r="B155" s="11">
         <f t="shared" si="3"/>
         <v>153</v>
@@ -7546,30 +7580,30 @@
       <c r="C155" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D155" s="9" t="s">
+      <c r="D155" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E155" s="10" t="s">
-        <v>331</v>
+      <c r="E155" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G155" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="I155" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="J155" s="9">
-        <v>1</v>
-      </c>
-      <c r="K155" s="9"/>
-    </row>
-    <row r="156" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>648</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="J155" s="7">
+        <v>2</v>
+      </c>
+      <c r="K155" s="7"/>
+    </row>
+    <row r="156" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B156" s="11">
         <f t="shared" si="3"/>
         <v>154</v>
@@ -7577,252 +7611,283 @@
       <c r="C156" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="D156" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E156" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="I156" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="J156" s="7">
-        <v>1</v>
-      </c>
-      <c r="K156" s="7"/>
+      <c r="E156" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="I156" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="J156" s="9">
+        <v>1</v>
+      </c>
+      <c r="K156" s="9"/>
     </row>
     <row r="157" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="11">
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-      <c r="C157" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="D157" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G157" s="10" t="s">
-        <v>665</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="I157" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J157" s="9">
-        <v>1</v>
-      </c>
-      <c r="K157" s="9"/>
+      <c r="C157" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="I157" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="J157" s="7">
+        <v>1</v>
+      </c>
+      <c r="K157" s="7"/>
     </row>
     <row r="158" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B158" s="11">
-        <f>ROW(B158) - ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>156</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>660</v>
+        <v>661</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>670</v>
       </c>
       <c r="F158" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G158" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J158" s="9">
+        <v>1</v>
+      </c>
+      <c r="K158" s="9"/>
+    </row>
+    <row r="159" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B159" s="11">
+        <f>ROW(B159) - ROW($B$2)</f>
+        <v>157</v>
+      </c>
+      <c r="C159" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="H158" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="I158" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J158" s="7">
+      <c r="D159" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J159" s="7">
         <v>6</v>
       </c>
-      <c r="K158" s="7"/>
-    </row>
-    <row r="159" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B159" s="11">
-        <f t="shared" ref="B159:B161" si="4">ROW(B159) - ROW($B$2)</f>
-        <v>157</v>
-      </c>
-      <c r="C159" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="D159" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G159" s="10" t="s">
-        <v>667</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="I159" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J159" s="9">
-        <v>1</v>
-      </c>
-      <c r="K159" s="19" t="s">
-        <v>669</v>
-      </c>
+      <c r="K159" s="7"/>
     </row>
     <row r="160" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B160" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="B160:B162" si="4">ROW(B160) - ROW($B$2)</f>
         <v>158</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="D160" s="7" t="s">
-        <v>670</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>646</v>
+        <v>661</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>650</v>
       </c>
       <c r="F160" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G160" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="H160" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="H160" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="I160" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J160" s="7">
-        <v>4</v>
-      </c>
-      <c r="K160" s="20" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="161" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I160" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J160" s="9">
+        <v>1</v>
+      </c>
+      <c r="K160" s="24" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B161" s="11">
         <f t="shared" si="4"/>
         <v>159</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D161" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="J161" s="7">
+        <v>4</v>
+      </c>
+      <c r="K161" s="25" t="s">
         <v>673</v>
       </c>
-      <c r="E161" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="I161" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J161" s="7"/>
-      <c r="K161" s="18" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="162" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B162" s="11">
-        <f>ROW(B162) - ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="C162" s="13" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="F162" s="9" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="I162" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J162" s="7">
-        <v>1</v>
-      </c>
-      <c r="K162" s="18" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="163" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="J162" s="7"/>
+      <c r="K162" s="23" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B163" s="11">
         <f>ROW(B163) - ROW($B$2)</f>
         <v>161</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>675</v>
+        <v>653</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="F163" s="9" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J163" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="K163" s="18" t="s">
-        <v>676</v>
+        <v>650</v>
+      </c>
+      <c r="J163" s="7">
+        <v>1</v>
+      </c>
+      <c r="K163" s="23" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B164" s="11">
+        <f>ROW(B164) - ROW($B$2)</f>
+        <v>162</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="K164" s="23" t="s">
+        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -7830,8 +7895,8 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K159" r:id="rId1"/>
-    <hyperlink ref="K160" r:id="rId2"/>
+    <hyperlink ref="K160" r:id="rId1"/>
+    <hyperlink ref="K161" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
+++ b/Design Files/Control-Boards-v2.0/BOM/Client-BOM-Control-Boards-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="681">
   <si>
     <t>#</t>
   </si>
@@ -2050,6 +2050,18 @@
   </si>
   <si>
     <t>Should be provided by client for testing</t>
+  </si>
+  <si>
+    <t>R339, R340, R341, R342, R343, R344</t>
+  </si>
+  <si>
+    <t>RES 560 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-07560RL</t>
+  </si>
+  <si>
+    <t>560R</t>
   </si>
 </sst>
 </file>
@@ -2605,7 +2617,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -4879,7 +4891,7 @@
     <row r="72" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="11">
-        <f t="shared" ref="B72:B135" si="2">ROW(B72) - ROW($B$2)</f>
+        <f t="shared" ref="B72:B136" si="2">ROW(B72) - ROW($B$2)</f>
         <v>70</v>
       </c>
       <c r="C72" s="13" t="s">
@@ -6805,194 +6817,194 @@
     <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="11">
-        <f t="shared" si="2"/>
+        <f>ROW(B132) - ROW($B$2)</f>
         <v>130</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>158</v>
+        <v>677</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F132" s="9" t="s">
-        <v>644</v>
+        <v>678</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>384</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>388</v>
+        <v>679</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>566</v>
+        <v>532</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>646</v>
+        <v>680</v>
       </c>
       <c r="J132" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K132" s="7"/>
     </row>
-    <row r="133" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="11">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
-      <c r="C133" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>310</v>
+      <c r="C133" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G133" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>567</v>
+      <c r="G133" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>566</v>
       </c>
       <c r="I133" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J133" s="9">
-        <v>1</v>
-      </c>
-      <c r="K133" s="9"/>
-    </row>
-    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J133" s="7">
+        <v>7</v>
+      </c>
+      <c r="K133" s="7"/>
+    </row>
+    <row r="134" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="11">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="C134" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>311</v>
+      <c r="C134" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G134" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>568</v>
+      <c r="G134" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="I134" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J134" s="7">
-        <v>1</v>
-      </c>
-      <c r="K134" s="7"/>
-    </row>
-    <row r="135" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J134" s="9">
+        <v>1</v>
+      </c>
+      <c r="K134" s="9"/>
+    </row>
+    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="11">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="C135" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>312</v>
+      <c r="C135" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>569</v>
+        <v>644</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>568</v>
       </c>
       <c r="I135" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J135" s="9">
-        <v>1</v>
-      </c>
-      <c r="K135" s="9"/>
-    </row>
-    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J135" s="7">
+        <v>1</v>
+      </c>
+      <c r="K135" s="7"/>
+    </row>
+    <row r="136" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="11">
-        <f t="shared" ref="B136:B157" si="3">ROW(B136) - ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D136" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="H136" s="7" t="s">
+      <c r="D136" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="H136" s="9" t="s">
         <v>569</v>
       </c>
       <c r="I136" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J136" s="7">
-        <v>1</v>
-      </c>
-      <c r="K136" s="7"/>
+      <c r="J136" s="9">
+        <v>1</v>
+      </c>
+      <c r="K136" s="9"/>
     </row>
     <row r="137" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="B137:B158" si="3">ROW(B137) - ROW($B$2)</f>
         <v>135</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D137" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>543</v>
+      <c r="D137" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>569</v>
       </c>
       <c r="I137" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J137" s="9">
-        <v>1</v>
-      </c>
-      <c r="K137" s="9"/>
+      <c r="J137" s="7">
+        <v>1</v>
+      </c>
+      <c r="K137" s="7"/>
     </row>
     <row r="138" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
@@ -7000,31 +7012,31 @@
         <f t="shared" si="3"/>
         <v>136</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="H138" s="7" t="s">
+      <c r="D138" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="H138" s="9" t="s">
         <v>543</v>
       </c>
       <c r="I138" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J138" s="7">
-        <v>1</v>
-      </c>
-      <c r="K138" s="7"/>
+      <c r="J138" s="9">
+        <v>1</v>
+      </c>
+      <c r="K138" s="9"/>
     </row>
     <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
@@ -7032,31 +7044,31 @@
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D139" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>570</v>
+      <c r="D139" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="I139" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J139" s="9">
-        <v>1</v>
-      </c>
-      <c r="K139" s="9"/>
+      <c r="J139" s="7">
+        <v>1</v>
+      </c>
+      <c r="K139" s="7"/>
     </row>
     <row r="140" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
@@ -7064,63 +7076,63 @@
         <f t="shared" si="3"/>
         <v>138</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D140" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>543</v>
+      <c r="D140" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="I140" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J140" s="7">
-        <v>1</v>
-      </c>
-      <c r="K140" s="7"/>
-    </row>
-    <row r="141" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J140" s="9">
+        <v>1</v>
+      </c>
+      <c r="K140" s="9"/>
+    </row>
+    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="11">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
-      <c r="C141" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="G141" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>545</v>
+      <c r="C141" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J141" s="9">
-        <v>2</v>
-      </c>
-      <c r="K141" s="9"/>
+      <c r="J141" s="7">
+        <v>1</v>
+      </c>
+      <c r="K141" s="7"/>
     </row>
     <row r="142" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
@@ -7128,63 +7140,63 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="C142" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>571</v>
+      <c r="C142" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>545</v>
       </c>
       <c r="I142" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J142" s="7">
-        <v>1</v>
-      </c>
-      <c r="K142" s="7"/>
-    </row>
-    <row r="143" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J142" s="9">
+        <v>2</v>
+      </c>
+      <c r="K142" s="9"/>
+    </row>
+    <row r="143" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="11">
         <f t="shared" si="3"/>
         <v>141</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D143" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>569</v>
+      <c r="D143" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>571</v>
       </c>
       <c r="I143" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J143" s="9">
-        <v>3</v>
-      </c>
-      <c r="K143" s="9"/>
+      <c r="J143" s="7">
+        <v>1</v>
+      </c>
+      <c r="K143" s="7"/>
     </row>
     <row r="144" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
@@ -7192,31 +7204,31 @@
         <f t="shared" si="3"/>
         <v>142</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D144" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="H144" s="7" t="s">
+      <c r="D144" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="H144" s="9" t="s">
         <v>569</v>
       </c>
       <c r="I144" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J144" s="7">
-        <v>2</v>
-      </c>
-      <c r="K144" s="7"/>
+      <c r="J144" s="9">
+        <v>3</v>
+      </c>
+      <c r="K144" s="9"/>
     </row>
     <row r="145" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
@@ -7224,31 +7236,31 @@
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C145" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D145" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="F145" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="H145" s="9" t="s">
+      <c r="D145" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="H145" s="7" t="s">
         <v>569</v>
       </c>
       <c r="I145" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J145" s="9">
-        <v>3</v>
-      </c>
-      <c r="K145" s="9"/>
+      <c r="J145" s="7">
+        <v>2</v>
+      </c>
+      <c r="K145" s="7"/>
     </row>
     <row r="146" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
@@ -7256,31 +7268,31 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D146" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>570</v>
+      <c r="D146" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I146" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J146" s="7">
-        <v>1</v>
-      </c>
-      <c r="K146" s="7"/>
+      <c r="J146" s="9">
+        <v>3</v>
+      </c>
+      <c r="K146" s="9"/>
     </row>
     <row r="147" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
@@ -7291,30 +7303,30 @@
       <c r="C147" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>542</v>
+      <c r="D147" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>570</v>
       </c>
       <c r="I147" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J147" s="9">
-        <v>1</v>
-      </c>
-      <c r="K147" s="9"/>
-    </row>
-    <row r="148" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J147" s="7">
+        <v>1</v>
+      </c>
+      <c r="K147" s="7"/>
+    </row>
+    <row r="148" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="11">
         <f t="shared" si="3"/>
@@ -7323,60 +7335,60 @@
       <c r="C148" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D148" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>324</v>
+      <c r="D148" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>323</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G148" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>572</v>
+      <c r="G148" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>542</v>
       </c>
       <c r="I148" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J148" s="7">
-        <v>8</v>
-      </c>
-      <c r="K148" s="7"/>
-    </row>
-    <row r="149" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J148" s="9">
+        <v>1</v>
+      </c>
+      <c r="K148" s="9"/>
+    </row>
+    <row r="149" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="11">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C149" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D149" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>325</v>
+      <c r="D149" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>324</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>569</v>
+        <v>644</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>572</v>
       </c>
       <c r="I149" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J149" s="9">
-        <v>1</v>
-      </c>
-      <c r="K149" s="9"/>
+      <c r="J149" s="7">
+        <v>8</v>
+      </c>
+      <c r="K149" s="7"/>
     </row>
     <row r="150" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
@@ -7384,31 +7396,31 @@
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
-      <c r="C150" s="12" t="s">
+      <c r="C150" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D150" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="H150" s="7" t="s">
+      <c r="D150" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="H150" s="9" t="s">
         <v>569</v>
       </c>
       <c r="I150" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J150" s="7">
-        <v>1</v>
-      </c>
-      <c r="K150" s="7"/>
+      <c r="J150" s="9">
+        <v>1</v>
+      </c>
+      <c r="K150" s="9"/>
     </row>
     <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
@@ -7416,31 +7428,31 @@
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
-      <c r="C151" s="13" t="s">
+      <c r="C151" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D151" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="H151" s="9" t="s">
+      <c r="D151" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H151" s="7" t="s">
         <v>569</v>
       </c>
       <c r="I151" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J151" s="9">
-        <v>1</v>
-      </c>
-      <c r="K151" s="9"/>
+      <c r="J151" s="7">
+        <v>1</v>
+      </c>
+      <c r="K151" s="7"/>
     </row>
     <row r="152" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
@@ -7448,31 +7460,31 @@
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
-      <c r="C152" s="12" t="s">
+      <c r="C152" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D152" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="H152" s="7" t="s">
+      <c r="D152" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="H152" s="9" t="s">
         <v>569</v>
       </c>
       <c r="I152" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J152" s="7">
-        <v>1</v>
-      </c>
-      <c r="K152" s="7"/>
+      <c r="J152" s="9">
+        <v>1</v>
+      </c>
+      <c r="K152" s="9"/>
     </row>
     <row r="153" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
@@ -7480,31 +7492,31 @@
         <f t="shared" si="3"/>
         <v>151</v>
       </c>
-      <c r="C153" s="13" t="s">
+      <c r="C153" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D153" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E153" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F153" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="G153" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="H153" s="9" t="s">
+      <c r="D153" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="H153" s="7" t="s">
         <v>569</v>
       </c>
       <c r="I153" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J153" s="9">
-        <v>1</v>
-      </c>
-      <c r="K153" s="9"/>
+      <c r="J153" s="7">
+        <v>1</v>
+      </c>
+      <c r="K153" s="7"/>
     </row>
     <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
@@ -7512,31 +7524,31 @@
         <f t="shared" si="3"/>
         <v>152</v>
       </c>
-      <c r="C154" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>330</v>
+      <c r="C154" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>573</v>
+        <v>405</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>569</v>
       </c>
       <c r="I154" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="J154" s="7">
-        <v>2</v>
-      </c>
-      <c r="K154" s="7"/>
+        <v>646</v>
+      </c>
+      <c r="J154" s="9">
+        <v>1</v>
+      </c>
+      <c r="K154" s="9"/>
     </row>
     <row r="155" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B155" s="11">
@@ -7546,30 +7558,30 @@
       <c r="C155" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D155" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>331</v>
+      <c r="D155" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G155" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="I155" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="J155" s="9">
-        <v>1</v>
-      </c>
-      <c r="K155" s="9"/>
-    </row>
-    <row r="156" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G155" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J155" s="7">
+        <v>2</v>
+      </c>
+      <c r="K155" s="7"/>
+    </row>
+    <row r="156" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B156" s="11">
         <f t="shared" si="3"/>
         <v>154</v>
@@ -7577,158 +7589,156 @@
       <c r="C156" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D156" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="I156" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="J156" s="7">
-        <v>1</v>
-      </c>
-      <c r="K156" s="7"/>
+      <c r="D156" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="I156" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="J156" s="9">
+        <v>1</v>
+      </c>
+      <c r="K156" s="9"/>
     </row>
     <row r="157" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="11">
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-      <c r="C157" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="D157" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="G157" s="10" t="s">
-        <v>665</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="I157" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J157" s="9">
-        <v>1</v>
-      </c>
-      <c r="K157" s="9"/>
+      <c r="C157" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="I157" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J157" s="7">
+        <v>1</v>
+      </c>
+      <c r="K157" s="7"/>
     </row>
     <row r="158" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B158" s="11">
-        <f>ROW(B158) - ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>156</v>
       </c>
       <c r="C158" s="13" t="s">
         <v>657</v>
       </c>
-      <c r="D158" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>660</v>
+      <c r="D158" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>666</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G158" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="H158" s="7" t="s">
-        <v>555</v>
+      <c r="G158" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>549</v>
       </c>
       <c r="I158" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="J158" s="7">
-        <v>6</v>
-      </c>
-      <c r="K158" s="7"/>
-    </row>
-    <row r="159" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J158" s="9">
+        <v>1</v>
+      </c>
+      <c r="K158" s="9"/>
+    </row>
+    <row r="159" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B159" s="11">
-        <f t="shared" ref="B159:B161" si="4">ROW(B159) - ROW($B$2)</f>
+        <f>ROW(B159) - ROW($B$2)</f>
         <v>157</v>
       </c>
       <c r="C159" s="13" t="s">
         <v>657</v>
       </c>
-      <c r="D159" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>646</v>
+      <c r="D159" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>660</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G159" s="10" t="s">
-        <v>667</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>668</v>
+      <c r="G159" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="I159" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="J159" s="9">
-        <v>1</v>
-      </c>
-      <c r="K159" s="19" t="s">
-        <v>669</v>
-      </c>
+      <c r="J159" s="7">
+        <v>6</v>
+      </c>
+      <c r="K159" s="7"/>
     </row>
     <row r="160" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B160" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="B160:B162" si="4">ROW(B160) - ROW($B$2)</f>
         <v>158</v>
       </c>
       <c r="C160" s="13" t="s">
         <v>657</v>
       </c>
-      <c r="D160" s="7" t="s">
-        <v>670</v>
-      </c>
-      <c r="E160" s="8" t="s">
+      <c r="D160" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E160" s="10" t="s">
         <v>646</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="G160" s="8" t="s">
-        <v>672</v>
+      <c r="G160" s="10" t="s">
+        <v>667</v>
       </c>
       <c r="H160" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="I160" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="J160" s="7">
-        <v>4</v>
-      </c>
-      <c r="K160" s="20" t="s">
+      <c r="I160" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J160" s="9">
+        <v>1</v>
+      </c>
+      <c r="K160" s="19" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="161" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B161" s="11">
         <f t="shared" si="4"/>
         <v>159</v>
@@ -7737,7 +7747,7 @@
         <v>657</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>646</v>
@@ -7746,38 +7756,40 @@
         <v>644</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>646</v>
+        <v>672</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>668</v>
       </c>
       <c r="I161" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J161" s="7"/>
-      <c r="K161" s="18" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="162" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J161" s="7">
+        <v>4</v>
+      </c>
+      <c r="K161" s="20" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B162" s="11">
-        <f>ROW(B162) - ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="C162" s="13" t="s">
         <v>657</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>644</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="H162" s="7" t="s">
         <v>646</v>
@@ -7785,14 +7797,12 @@
       <c r="I162" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J162" s="7">
-        <v>1</v>
-      </c>
+      <c r="J162" s="7"/>
       <c r="K162" s="18" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="163" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B163" s="11">
         <f>ROW(B163) - ROW($B$2)</f>
         <v>161</v>
@@ -7801,16 +7811,16 @@
         <v>657</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>644</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="H163" s="7" t="s">
         <v>646</v>
@@ -7818,10 +7828,43 @@
       <c r="I163" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J163" s="7" t="s">
-        <v>646</v>
+      <c r="J163" s="7">
+        <v>1</v>
       </c>
       <c r="K163" s="18" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B164" s="11">
+        <f>ROW(B164) - ROW($B$2)</f>
+        <v>162</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="K164" s="18" t="s">
         <v>676</v>
       </c>
     </row>
@@ -7830,8 +7873,8 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K159" r:id="rId1"/>
-    <hyperlink ref="K160" r:id="rId2"/>
+    <hyperlink ref="K160" r:id="rId1"/>
+    <hyperlink ref="K161" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
